--- a/processing/processing_data_5.xlsx
+++ b/processing/processing_data_5.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4229" uniqueCount="637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4499" uniqueCount="637">
   <si>
     <t>Category</t>
   </si>
@@ -1909,10 +1909,10 @@
     <t>Excellent</t>
   </si>
   <si>
+    <t>Poor</t>
+  </si>
+  <si>
     <t>Good</t>
-  </si>
-  <si>
-    <t>Poor</t>
   </si>
   <si>
     <t>Big Brand</t>
@@ -3373,11 +3373,17 @@
       <c r="I21" t="s">
         <v>629</v>
       </c>
+      <c r="J21" t="s">
+        <v>631</v>
+      </c>
       <c r="K21" t="s">
         <v>633</v>
       </c>
       <c r="L21" t="s">
         <v>635</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
       </c>
       <c r="N21">
         <v>529</v>
@@ -5117,7 +5123,7 @@
         <v>626</v>
       </c>
       <c r="J54" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K54" t="s">
         <v>634</v>
@@ -5593,11 +5599,17 @@
       <c r="I63" t="s">
         <v>626</v>
       </c>
+      <c r="J63" t="s">
+        <v>631</v>
+      </c>
       <c r="K63" t="s">
         <v>633</v>
       </c>
       <c r="L63" t="s">
         <v>636</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
       </c>
       <c r="N63">
         <v>73</v>
@@ -6330,7 +6342,7 @@
         <v>626</v>
       </c>
       <c r="J77" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K77" t="s">
         <v>634</v>
@@ -7973,7 +7985,7 @@
         <v>626</v>
       </c>
       <c r="J108" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K108" t="s">
         <v>634</v>
@@ -8026,7 +8038,7 @@
         <v>626</v>
       </c>
       <c r="J109" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K109" t="s">
         <v>633</v>
@@ -8344,7 +8356,7 @@
         <v>626</v>
       </c>
       <c r="J115" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K115" t="s">
         <v>634</v>
@@ -8396,11 +8408,17 @@
       <c r="I116" t="s">
         <v>626</v>
       </c>
+      <c r="J116" t="s">
+        <v>631</v>
+      </c>
       <c r="K116" t="s">
         <v>634</v>
       </c>
       <c r="L116" t="s">
         <v>635</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
       </c>
       <c r="N116">
         <v>28</v>
@@ -9026,11 +9044,17 @@
       <c r="I128" t="s">
         <v>626</v>
       </c>
+      <c r="J128" t="s">
+        <v>631</v>
+      </c>
       <c r="K128" t="s">
         <v>634</v>
       </c>
       <c r="L128" t="s">
         <v>635</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
       </c>
       <c r="N128">
         <v>20</v>
@@ -9180,7 +9204,7 @@
         <v>626</v>
       </c>
       <c r="J131" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K131" t="s">
         <v>634</v>
@@ -9339,7 +9363,7 @@
         <v>626</v>
       </c>
       <c r="J134" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K134" t="s">
         <v>634</v>
@@ -9392,7 +9416,7 @@
         <v>626</v>
       </c>
       <c r="J135" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K135" t="s">
         <v>634</v>
@@ -9710,7 +9734,7 @@
         <v>626</v>
       </c>
       <c r="J141" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K141" t="s">
         <v>634</v>
@@ -9762,11 +9786,17 @@
       <c r="I142" t="s">
         <v>626</v>
       </c>
+      <c r="J142" t="s">
+        <v>631</v>
+      </c>
       <c r="K142" t="s">
         <v>634</v>
       </c>
       <c r="L142" t="s">
         <v>635</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
       </c>
       <c r="N142">
         <v>14</v>
@@ -9809,11 +9839,17 @@
       <c r="I143" t="s">
         <v>626</v>
       </c>
+      <c r="J143" t="s">
+        <v>631</v>
+      </c>
       <c r="K143" t="s">
         <v>633</v>
       </c>
       <c r="L143" t="s">
         <v>636</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
       </c>
       <c r="N143">
         <v>13</v>
@@ -9856,11 +9892,17 @@
       <c r="I144" t="s">
         <v>626</v>
       </c>
+      <c r="J144" t="s">
+        <v>631</v>
+      </c>
       <c r="K144" t="s">
         <v>633</v>
       </c>
       <c r="L144" t="s">
         <v>635</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
       </c>
       <c r="N144">
         <v>13</v>
@@ -9903,11 +9945,17 @@
       <c r="I145" t="s">
         <v>626</v>
       </c>
+      <c r="J145" t="s">
+        <v>631</v>
+      </c>
       <c r="K145" t="s">
         <v>633</v>
       </c>
       <c r="L145" t="s">
         <v>635</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
       </c>
       <c r="N145">
         <v>13</v>
@@ -9950,11 +9998,17 @@
       <c r="I146" t="s">
         <v>626</v>
       </c>
+      <c r="J146" t="s">
+        <v>631</v>
+      </c>
       <c r="K146" t="s">
         <v>633</v>
       </c>
       <c r="L146" t="s">
         <v>635</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
       </c>
       <c r="N146">
         <v>13</v>
@@ -9997,11 +10051,17 @@
       <c r="I147" t="s">
         <v>626</v>
       </c>
+      <c r="J147" t="s">
+        <v>631</v>
+      </c>
       <c r="K147" t="s">
         <v>633</v>
       </c>
       <c r="L147" t="s">
         <v>636</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
       </c>
       <c r="N147">
         <v>13</v>
@@ -10044,11 +10104,17 @@
       <c r="I148" t="s">
         <v>626</v>
       </c>
+      <c r="J148" t="s">
+        <v>631</v>
+      </c>
       <c r="K148" t="s">
         <v>633</v>
       </c>
       <c r="L148" t="s">
         <v>636</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
       </c>
       <c r="N148">
         <v>13</v>
@@ -10091,11 +10157,17 @@
       <c r="I149" t="s">
         <v>626</v>
       </c>
+      <c r="J149" t="s">
+        <v>631</v>
+      </c>
       <c r="K149" t="s">
         <v>633</v>
       </c>
       <c r="L149" t="s">
         <v>635</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
       </c>
       <c r="N149">
         <v>13</v>
@@ -10138,11 +10210,17 @@
       <c r="I150" t="s">
         <v>626</v>
       </c>
+      <c r="J150" t="s">
+        <v>631</v>
+      </c>
       <c r="K150" t="s">
         <v>633</v>
       </c>
       <c r="L150" t="s">
         <v>635</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
       </c>
       <c r="N150">
         <v>13</v>
@@ -10185,11 +10263,17 @@
       <c r="I151" t="s">
         <v>626</v>
       </c>
+      <c r="J151" t="s">
+        <v>631</v>
+      </c>
       <c r="K151" t="s">
         <v>634</v>
       </c>
       <c r="L151" t="s">
         <v>635</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
       </c>
       <c r="N151">
         <v>13</v>
@@ -10232,11 +10316,17 @@
       <c r="I152" t="s">
         <v>626</v>
       </c>
+      <c r="J152" t="s">
+        <v>631</v>
+      </c>
       <c r="K152" t="s">
         <v>633</v>
       </c>
       <c r="L152" t="s">
         <v>636</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
       </c>
       <c r="N152">
         <v>13</v>
@@ -10333,7 +10423,7 @@
         <v>626</v>
       </c>
       <c r="J154" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K154" t="s">
         <v>634</v>
@@ -10544,11 +10634,17 @@
       <c r="I158" t="s">
         <v>626</v>
       </c>
+      <c r="J158" t="s">
+        <v>631</v>
+      </c>
       <c r="K158" t="s">
         <v>633</v>
       </c>
       <c r="L158" t="s">
         <v>635</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
       </c>
       <c r="N158">
         <v>13</v>
@@ -10751,7 +10847,7 @@
         <v>626</v>
       </c>
       <c r="J162" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K162" t="s">
         <v>634</v>
@@ -10803,11 +10899,17 @@
       <c r="I163" t="s">
         <v>626</v>
       </c>
+      <c r="J163" t="s">
+        <v>631</v>
+      </c>
       <c r="K163" t="s">
         <v>634</v>
       </c>
       <c r="L163" t="s">
         <v>635</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
       </c>
       <c r="N163">
         <v>12</v>
@@ -10850,11 +10952,17 @@
       <c r="I164" t="s">
         <v>626</v>
       </c>
+      <c r="J164" t="s">
+        <v>631</v>
+      </c>
       <c r="K164" t="s">
         <v>634</v>
       </c>
       <c r="L164" t="s">
         <v>635</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
       </c>
       <c r="N164">
         <v>12</v>
@@ -11534,7 +11642,7 @@
         <v>626</v>
       </c>
       <c r="J177" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K177" t="s">
         <v>634</v>
@@ -11587,7 +11695,7 @@
         <v>626</v>
       </c>
       <c r="J178" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K178" t="s">
         <v>634</v>
@@ -11639,11 +11747,17 @@
       <c r="I179" t="s">
         <v>626</v>
       </c>
+      <c r="J179" t="s">
+        <v>631</v>
+      </c>
       <c r="K179" t="s">
         <v>634</v>
       </c>
       <c r="L179" t="s">
         <v>635</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
       </c>
       <c r="N179">
         <v>10</v>
@@ -11686,11 +11800,17 @@
       <c r="I180" t="s">
         <v>626</v>
       </c>
+      <c r="J180" t="s">
+        <v>631</v>
+      </c>
       <c r="K180" t="s">
         <v>634</v>
       </c>
       <c r="L180" t="s">
         <v>635</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
       </c>
       <c r="N180">
         <v>10</v>
@@ -11786,11 +11906,17 @@
       <c r="I182" t="s">
         <v>626</v>
       </c>
+      <c r="J182" t="s">
+        <v>631</v>
+      </c>
       <c r="K182" t="s">
         <v>633</v>
       </c>
       <c r="L182" t="s">
         <v>635</v>
+      </c>
+      <c r="M182">
+        <v>0</v>
       </c>
       <c r="N182">
         <v>9</v>
@@ -11834,7 +11960,7 @@
         <v>626</v>
       </c>
       <c r="J183" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K183" t="s">
         <v>633</v>
@@ -12257,11 +12383,17 @@
       <c r="I191" t="s">
         <v>626</v>
       </c>
+      <c r="J191" t="s">
+        <v>631</v>
+      </c>
       <c r="K191" t="s">
         <v>634</v>
       </c>
       <c r="L191" t="s">
         <v>635</v>
+      </c>
+      <c r="M191">
+        <v>0</v>
       </c>
       <c r="N191">
         <v>8</v>
@@ -12304,11 +12436,17 @@
       <c r="I192" t="s">
         <v>626</v>
       </c>
+      <c r="J192" t="s">
+        <v>631</v>
+      </c>
       <c r="K192" t="s">
         <v>634</v>
       </c>
       <c r="L192" t="s">
         <v>635</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
       </c>
       <c r="N192">
         <v>7</v>
@@ -12351,11 +12489,17 @@
       <c r="I193" t="s">
         <v>626</v>
       </c>
+      <c r="J193" t="s">
+        <v>631</v>
+      </c>
       <c r="K193" t="s">
         <v>634</v>
       </c>
       <c r="L193" t="s">
         <v>635</v>
+      </c>
+      <c r="M193">
+        <v>0</v>
       </c>
       <c r="N193">
         <v>7</v>
@@ -12398,11 +12542,17 @@
       <c r="I194" t="s">
         <v>626</v>
       </c>
+      <c r="J194" t="s">
+        <v>631</v>
+      </c>
       <c r="K194" t="s">
         <v>634</v>
       </c>
       <c r="L194" t="s">
         <v>635</v>
+      </c>
+      <c r="M194">
+        <v>0</v>
       </c>
       <c r="N194">
         <v>7</v>
@@ -12445,11 +12595,17 @@
       <c r="I195" t="s">
         <v>626</v>
       </c>
+      <c r="J195" t="s">
+        <v>631</v>
+      </c>
       <c r="K195" t="s">
         <v>634</v>
       </c>
       <c r="L195" t="s">
         <v>635</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
       </c>
       <c r="N195">
         <v>7</v>
@@ -12492,11 +12648,17 @@
       <c r="I196" t="s">
         <v>626</v>
       </c>
+      <c r="J196" t="s">
+        <v>631</v>
+      </c>
       <c r="K196" t="s">
         <v>634</v>
       </c>
       <c r="L196" t="s">
         <v>635</v>
+      </c>
+      <c r="M196">
+        <v>0</v>
       </c>
       <c r="N196">
         <v>7</v>
@@ -12539,11 +12701,17 @@
       <c r="I197" t="s">
         <v>626</v>
       </c>
+      <c r="J197" t="s">
+        <v>631</v>
+      </c>
       <c r="K197" t="s">
         <v>634</v>
       </c>
       <c r="L197" t="s">
         <v>635</v>
+      </c>
+      <c r="M197">
+        <v>0</v>
       </c>
       <c r="N197">
         <v>7</v>
@@ -12586,11 +12754,17 @@
       <c r="I198" t="s">
         <v>626</v>
       </c>
+      <c r="J198" t="s">
+        <v>631</v>
+      </c>
       <c r="K198" t="s">
         <v>633</v>
       </c>
       <c r="L198" t="s">
         <v>635</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
       </c>
       <c r="N198">
         <v>7</v>
@@ -12633,11 +12807,17 @@
       <c r="I199" t="s">
         <v>626</v>
       </c>
+      <c r="J199" t="s">
+        <v>631</v>
+      </c>
       <c r="K199" t="s">
         <v>634</v>
       </c>
       <c r="L199" t="s">
         <v>635</v>
+      </c>
+      <c r="M199">
+        <v>0</v>
       </c>
       <c r="N199">
         <v>7</v>
@@ -12680,11 +12860,17 @@
       <c r="I200" t="s">
         <v>626</v>
       </c>
+      <c r="J200" t="s">
+        <v>631</v>
+      </c>
       <c r="K200" t="s">
         <v>634</v>
       </c>
       <c r="L200" t="s">
         <v>635</v>
+      </c>
+      <c r="M200">
+        <v>0</v>
       </c>
       <c r="N200">
         <v>7</v>
@@ -12727,11 +12913,17 @@
       <c r="I201" t="s">
         <v>626</v>
       </c>
+      <c r="J201" t="s">
+        <v>631</v>
+      </c>
       <c r="K201" t="s">
         <v>633</v>
       </c>
       <c r="L201" t="s">
         <v>635</v>
+      </c>
+      <c r="M201">
+        <v>0</v>
       </c>
       <c r="N201">
         <v>7</v>
@@ -12774,11 +12966,17 @@
       <c r="I202" t="s">
         <v>626</v>
       </c>
+      <c r="J202" t="s">
+        <v>631</v>
+      </c>
       <c r="K202" t="s">
         <v>634</v>
       </c>
       <c r="L202" t="s">
         <v>635</v>
+      </c>
+      <c r="M202">
+        <v>0</v>
       </c>
       <c r="N202">
         <v>7</v>
@@ -12821,11 +13019,17 @@
       <c r="I203" t="s">
         <v>626</v>
       </c>
+      <c r="J203" t="s">
+        <v>631</v>
+      </c>
       <c r="K203" t="s">
         <v>634</v>
       </c>
       <c r="L203" t="s">
         <v>635</v>
+      </c>
+      <c r="M203">
+        <v>0</v>
       </c>
       <c r="N203">
         <v>7</v>
@@ -12868,11 +13072,17 @@
       <c r="I204" t="s">
         <v>626</v>
       </c>
+      <c r="J204" t="s">
+        <v>631</v>
+      </c>
       <c r="K204" t="s">
         <v>634</v>
       </c>
       <c r="L204" t="s">
         <v>635</v>
+      </c>
+      <c r="M204">
+        <v>0</v>
       </c>
       <c r="N204">
         <v>7</v>
@@ -12916,7 +13126,7 @@
         <v>626</v>
       </c>
       <c r="J205" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K205" t="s">
         <v>634</v>
@@ -12969,7 +13179,7 @@
         <v>626</v>
       </c>
       <c r="J206" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="K206" t="s">
         <v>634</v>
@@ -13445,11 +13655,17 @@
       <c r="I215" t="s">
         <v>626</v>
       </c>
+      <c r="J215" t="s">
+        <v>631</v>
+      </c>
       <c r="K215" t="s">
         <v>633</v>
       </c>
       <c r="L215" t="s">
         <v>635</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
       </c>
       <c r="N215">
         <v>6</v>
@@ -13492,11 +13708,17 @@
       <c r="I216" t="s">
         <v>626</v>
       </c>
+      <c r="J216" t="s">
+        <v>631</v>
+      </c>
       <c r="K216" t="s">
         <v>634</v>
       </c>
       <c r="L216" t="s">
         <v>635</v>
+      </c>
+      <c r="M216">
+        <v>0</v>
       </c>
       <c r="N216">
         <v>6</v>
@@ -13539,11 +13761,17 @@
       <c r="I217" t="s">
         <v>626</v>
       </c>
+      <c r="J217" t="s">
+        <v>631</v>
+      </c>
       <c r="K217" t="s">
         <v>634</v>
       </c>
       <c r="L217" t="s">
         <v>635</v>
+      </c>
+      <c r="M217">
+        <v>0</v>
       </c>
       <c r="N217">
         <v>6</v>
@@ -14010,11 +14238,17 @@
       <c r="I226" t="s">
         <v>626</v>
       </c>
+      <c r="J226" t="s">
+        <v>631</v>
+      </c>
       <c r="K226" t="s">
         <v>634</v>
       </c>
       <c r="L226" t="s">
         <v>635</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
       </c>
       <c r="N226">
         <v>5</v>
@@ -14057,11 +14291,17 @@
       <c r="I227" t="s">
         <v>626</v>
       </c>
+      <c r="J227" t="s">
+        <v>631</v>
+      </c>
       <c r="K227" t="s">
         <v>634</v>
       </c>
       <c r="L227" t="s">
         <v>635</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
       </c>
       <c r="N227">
         <v>5</v>
@@ -14104,11 +14344,17 @@
       <c r="I228" t="s">
         <v>626</v>
       </c>
+      <c r="J228" t="s">
+        <v>631</v>
+      </c>
       <c r="K228" t="s">
         <v>634</v>
       </c>
       <c r="L228" t="s">
         <v>635</v>
+      </c>
+      <c r="M228">
+        <v>0</v>
       </c>
       <c r="N228">
         <v>5</v>
@@ -14151,11 +14397,17 @@
       <c r="I229" t="s">
         <v>626</v>
       </c>
+      <c r="J229" t="s">
+        <v>631</v>
+      </c>
       <c r="K229" t="s">
         <v>634</v>
       </c>
       <c r="L229" t="s">
         <v>635</v>
+      </c>
+      <c r="M229">
+        <v>0</v>
       </c>
       <c r="N229">
         <v>5</v>
@@ -14198,11 +14450,17 @@
       <c r="I230" t="s">
         <v>626</v>
       </c>
+      <c r="J230" t="s">
+        <v>631</v>
+      </c>
       <c r="K230" t="s">
         <v>634</v>
       </c>
       <c r="L230" t="s">
         <v>635</v>
+      </c>
+      <c r="M230">
+        <v>0</v>
       </c>
       <c r="N230">
         <v>5</v>
@@ -14245,11 +14503,17 @@
       <c r="I231" t="s">
         <v>626</v>
       </c>
+      <c r="J231" t="s">
+        <v>631</v>
+      </c>
       <c r="K231" t="s">
         <v>633</v>
       </c>
       <c r="L231" t="s">
         <v>636</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
       </c>
       <c r="N231">
         <v>5</v>
@@ -14293,7 +14557,7 @@
         <v>626</v>
       </c>
       <c r="J232" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K232" t="s">
         <v>634</v>
@@ -14822,11 +15086,17 @@
       <c r="I242" t="s">
         <v>626</v>
       </c>
+      <c r="J242" t="s">
+        <v>631</v>
+      </c>
       <c r="K242" t="s">
         <v>634</v>
       </c>
       <c r="L242" t="s">
         <v>635</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
       </c>
       <c r="N242">
         <v>4</v>
@@ -14869,11 +15139,17 @@
       <c r="I243" t="s">
         <v>626</v>
       </c>
+      <c r="J243" t="s">
+        <v>631</v>
+      </c>
       <c r="K243" t="s">
         <v>634</v>
       </c>
       <c r="L243" t="s">
         <v>635</v>
+      </c>
+      <c r="M243">
+        <v>0</v>
       </c>
       <c r="N243">
         <v>4</v>
@@ -14916,11 +15192,17 @@
       <c r="I244" t="s">
         <v>626</v>
       </c>
+      <c r="J244" t="s">
+        <v>631</v>
+      </c>
       <c r="K244" t="s">
         <v>634</v>
       </c>
       <c r="L244" t="s">
         <v>635</v>
+      </c>
+      <c r="M244">
+        <v>0</v>
       </c>
       <c r="N244">
         <v>4</v>
@@ -14963,11 +15245,17 @@
       <c r="I245" t="s">
         <v>626</v>
       </c>
+      <c r="J245" t="s">
+        <v>631</v>
+      </c>
       <c r="K245" t="s">
         <v>634</v>
       </c>
       <c r="L245" t="s">
         <v>635</v>
+      </c>
+      <c r="M245">
+        <v>0</v>
       </c>
       <c r="N245">
         <v>4</v>
@@ -15010,11 +15298,17 @@
       <c r="I246" t="s">
         <v>626</v>
       </c>
+      <c r="J246" t="s">
+        <v>631</v>
+      </c>
       <c r="K246" t="s">
         <v>634</v>
       </c>
       <c r="L246" t="s">
         <v>635</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
       </c>
       <c r="N246">
         <v>4</v>
@@ -15057,11 +15351,17 @@
       <c r="I247" t="s">
         <v>626</v>
       </c>
+      <c r="J247" t="s">
+        <v>631</v>
+      </c>
       <c r="K247" t="s">
         <v>633</v>
       </c>
       <c r="L247" t="s">
         <v>635</v>
+      </c>
+      <c r="M247">
+        <v>0</v>
       </c>
       <c r="N247">
         <v>4</v>
@@ -15104,11 +15404,17 @@
       <c r="I248" t="s">
         <v>626</v>
       </c>
+      <c r="J248" t="s">
+        <v>631</v>
+      </c>
       <c r="K248" t="s">
         <v>634</v>
       </c>
       <c r="L248" t="s">
         <v>636</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
       </c>
       <c r="N248">
         <v>4</v>
@@ -15151,11 +15457,17 @@
       <c r="I249" t="s">
         <v>626</v>
       </c>
+      <c r="J249" t="s">
+        <v>631</v>
+      </c>
       <c r="K249" t="s">
         <v>634</v>
       </c>
       <c r="L249" t="s">
         <v>635</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
       </c>
       <c r="N249">
         <v>4</v>
@@ -15357,11 +15669,17 @@
       <c r="I253" t="s">
         <v>626</v>
       </c>
+      <c r="J253" t="s">
+        <v>631</v>
+      </c>
       <c r="K253" t="s">
         <v>634</v>
       </c>
       <c r="L253" t="s">
         <v>635</v>
+      </c>
+      <c r="M253">
+        <v>0</v>
       </c>
       <c r="N253">
         <v>4</v>
@@ -15404,11 +15722,17 @@
       <c r="I254" t="s">
         <v>626</v>
       </c>
+      <c r="J254" t="s">
+        <v>631</v>
+      </c>
       <c r="K254" t="s">
         <v>634</v>
       </c>
       <c r="L254" t="s">
         <v>635</v>
+      </c>
+      <c r="M254">
+        <v>0</v>
       </c>
       <c r="N254">
         <v>3</v>
@@ -15451,11 +15775,17 @@
       <c r="I255" t="s">
         <v>626</v>
       </c>
+      <c r="J255" t="s">
+        <v>631</v>
+      </c>
       <c r="K255" t="s">
         <v>634</v>
       </c>
       <c r="L255" t="s">
         <v>635</v>
+      </c>
+      <c r="M255">
+        <v>0</v>
       </c>
       <c r="N255">
         <v>3</v>
@@ -15498,11 +15828,17 @@
       <c r="I256" t="s">
         <v>626</v>
       </c>
+      <c r="J256" t="s">
+        <v>631</v>
+      </c>
       <c r="K256" t="s">
         <v>634</v>
       </c>
       <c r="L256" t="s">
         <v>635</v>
+      </c>
+      <c r="M256">
+        <v>0</v>
       </c>
       <c r="N256">
         <v>3</v>
@@ -15545,11 +15881,17 @@
       <c r="I257" t="s">
         <v>626</v>
       </c>
+      <c r="J257" t="s">
+        <v>631</v>
+      </c>
       <c r="K257" t="s">
         <v>633</v>
       </c>
       <c r="L257" t="s">
         <v>635</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
       </c>
       <c r="N257">
         <v>3</v>
@@ -15592,11 +15934,17 @@
       <c r="I258" t="s">
         <v>626</v>
       </c>
+      <c r="J258" t="s">
+        <v>631</v>
+      </c>
       <c r="K258" t="s">
         <v>633</v>
       </c>
       <c r="L258" t="s">
         <v>635</v>
+      </c>
+      <c r="M258">
+        <v>0</v>
       </c>
       <c r="N258">
         <v>3</v>
@@ -15639,11 +15987,17 @@
       <c r="I259" t="s">
         <v>626</v>
       </c>
+      <c r="J259" t="s">
+        <v>631</v>
+      </c>
       <c r="K259" t="s">
         <v>634</v>
       </c>
       <c r="L259" t="s">
         <v>635</v>
+      </c>
+      <c r="M259">
+        <v>0</v>
       </c>
       <c r="N259">
         <v>3</v>
@@ -15686,11 +16040,17 @@
       <c r="I260" t="s">
         <v>626</v>
       </c>
+      <c r="J260" t="s">
+        <v>631</v>
+      </c>
       <c r="K260" t="s">
         <v>634</v>
       </c>
       <c r="L260" t="s">
         <v>635</v>
+      </c>
+      <c r="M260">
+        <v>0</v>
       </c>
       <c r="N260">
         <v>3</v>
@@ -15733,11 +16093,17 @@
       <c r="I261" t="s">
         <v>626</v>
       </c>
+      <c r="J261" t="s">
+        <v>631</v>
+      </c>
       <c r="K261" t="s">
         <v>634</v>
       </c>
       <c r="L261" t="s">
         <v>635</v>
+      </c>
+      <c r="M261">
+        <v>0</v>
       </c>
       <c r="N261">
         <v>3</v>
@@ -15780,11 +16146,17 @@
       <c r="I262" t="s">
         <v>626</v>
       </c>
+      <c r="J262" t="s">
+        <v>631</v>
+      </c>
       <c r="K262" t="s">
         <v>633</v>
       </c>
       <c r="L262" t="s">
         <v>635</v>
+      </c>
+      <c r="M262">
+        <v>0</v>
       </c>
       <c r="N262">
         <v>3</v>
@@ -15827,11 +16199,17 @@
       <c r="I263" t="s">
         <v>626</v>
       </c>
+      <c r="J263" t="s">
+        <v>631</v>
+      </c>
       <c r="K263" t="s">
         <v>634</v>
       </c>
       <c r="L263" t="s">
         <v>635</v>
+      </c>
+      <c r="M263">
+        <v>0</v>
       </c>
       <c r="N263">
         <v>3</v>
@@ -15874,11 +16252,17 @@
       <c r="I264" t="s">
         <v>626</v>
       </c>
+      <c r="J264" t="s">
+        <v>631</v>
+      </c>
       <c r="K264" t="s">
         <v>633</v>
       </c>
       <c r="L264" t="s">
         <v>635</v>
+      </c>
+      <c r="M264">
+        <v>0</v>
       </c>
       <c r="N264">
         <v>3</v>
@@ -15921,11 +16305,17 @@
       <c r="I265" t="s">
         <v>626</v>
       </c>
+      <c r="J265" t="s">
+        <v>631</v>
+      </c>
       <c r="K265" t="s">
         <v>633</v>
       </c>
       <c r="L265" t="s">
         <v>635</v>
+      </c>
+      <c r="M265">
+        <v>0</v>
       </c>
       <c r="N265">
         <v>3</v>
@@ -16022,7 +16412,7 @@
         <v>626</v>
       </c>
       <c r="J267" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K267" t="s">
         <v>633</v>
@@ -16393,7 +16783,7 @@
         <v>626</v>
       </c>
       <c r="J274" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K274" t="s">
         <v>634</v>
@@ -16445,11 +16835,17 @@
       <c r="I275" t="s">
         <v>626</v>
       </c>
+      <c r="J275" t="s">
+        <v>631</v>
+      </c>
       <c r="K275" t="s">
         <v>634</v>
       </c>
       <c r="L275" t="s">
         <v>635</v>
+      </c>
+      <c r="M275">
+        <v>0</v>
       </c>
       <c r="N275">
         <v>2</v>
@@ -16492,11 +16888,17 @@
       <c r="I276" t="s">
         <v>626</v>
       </c>
+      <c r="J276" t="s">
+        <v>631</v>
+      </c>
       <c r="K276" t="s">
         <v>634</v>
       </c>
       <c r="L276" t="s">
         <v>636</v>
+      </c>
+      <c r="M276">
+        <v>0</v>
       </c>
       <c r="N276">
         <v>2</v>
@@ -16539,11 +16941,17 @@
       <c r="I277" t="s">
         <v>626</v>
       </c>
+      <c r="J277" t="s">
+        <v>631</v>
+      </c>
       <c r="K277" t="s">
         <v>634</v>
       </c>
       <c r="L277" t="s">
         <v>635</v>
+      </c>
+      <c r="M277">
+        <v>0</v>
       </c>
       <c r="N277">
         <v>2</v>
@@ -16586,11 +16994,17 @@
       <c r="I278" t="s">
         <v>626</v>
       </c>
+      <c r="J278" t="s">
+        <v>631</v>
+      </c>
       <c r="K278" t="s">
         <v>634</v>
       </c>
       <c r="L278" t="s">
         <v>635</v>
+      </c>
+      <c r="M278">
+        <v>0</v>
       </c>
       <c r="N278">
         <v>2</v>
@@ -16633,11 +17047,17 @@
       <c r="I279" t="s">
         <v>626</v>
       </c>
+      <c r="J279" t="s">
+        <v>631</v>
+      </c>
       <c r="K279" t="s">
         <v>634</v>
       </c>
       <c r="L279" t="s">
         <v>635</v>
+      </c>
+      <c r="M279">
+        <v>0</v>
       </c>
       <c r="N279">
         <v>2</v>
@@ -16680,11 +17100,17 @@
       <c r="I280" t="s">
         <v>626</v>
       </c>
+      <c r="J280" t="s">
+        <v>631</v>
+      </c>
       <c r="K280" t="s">
         <v>634</v>
       </c>
       <c r="L280" t="s">
         <v>635</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
       </c>
       <c r="N280">
         <v>2</v>
@@ -16727,11 +17153,17 @@
       <c r="I281" t="s">
         <v>626</v>
       </c>
+      <c r="J281" t="s">
+        <v>631</v>
+      </c>
       <c r="K281" t="s">
         <v>633</v>
       </c>
       <c r="L281" t="s">
         <v>636</v>
+      </c>
+      <c r="M281">
+        <v>0</v>
       </c>
       <c r="N281">
         <v>2</v>
@@ -16774,11 +17206,17 @@
       <c r="I282" t="s">
         <v>626</v>
       </c>
+      <c r="J282" t="s">
+        <v>631</v>
+      </c>
       <c r="K282" t="s">
         <v>634</v>
       </c>
       <c r="L282" t="s">
         <v>635</v>
+      </c>
+      <c r="M282">
+        <v>0</v>
       </c>
       <c r="N282">
         <v>2</v>
@@ -16821,11 +17259,17 @@
       <c r="I283" t="s">
         <v>626</v>
       </c>
+      <c r="J283" t="s">
+        <v>631</v>
+      </c>
       <c r="K283" t="s">
         <v>634</v>
       </c>
       <c r="L283" t="s">
         <v>635</v>
+      </c>
+      <c r="M283">
+        <v>0</v>
       </c>
       <c r="N283">
         <v>2</v>
@@ -16868,11 +17312,17 @@
       <c r="I284" t="s">
         <v>626</v>
       </c>
+      <c r="J284" t="s">
+        <v>631</v>
+      </c>
       <c r="K284" t="s">
         <v>634</v>
       </c>
       <c r="L284" t="s">
         <v>635</v>
+      </c>
+      <c r="M284">
+        <v>0</v>
       </c>
       <c r="N284">
         <v>2</v>
@@ -16915,11 +17365,17 @@
       <c r="I285" t="s">
         <v>626</v>
       </c>
+      <c r="J285" t="s">
+        <v>631</v>
+      </c>
       <c r="K285" t="s">
         <v>634</v>
       </c>
       <c r="L285" t="s">
         <v>635</v>
+      </c>
+      <c r="M285">
+        <v>0</v>
       </c>
       <c r="N285">
         <v>2</v>
@@ -16962,11 +17418,17 @@
       <c r="I286" t="s">
         <v>626</v>
       </c>
+      <c r="J286" t="s">
+        <v>631</v>
+      </c>
       <c r="K286" t="s">
         <v>634</v>
       </c>
       <c r="L286" t="s">
         <v>635</v>
+      </c>
+      <c r="M286">
+        <v>0</v>
       </c>
       <c r="N286">
         <v>2</v>
@@ -17009,11 +17471,17 @@
       <c r="I287" t="s">
         <v>626</v>
       </c>
+      <c r="J287" t="s">
+        <v>631</v>
+      </c>
       <c r="K287" t="s">
         <v>634</v>
       </c>
       <c r="L287" t="s">
         <v>636</v>
+      </c>
+      <c r="M287">
+        <v>0</v>
       </c>
       <c r="N287">
         <v>2</v>
@@ -17056,11 +17524,17 @@
       <c r="I288" t="s">
         <v>626</v>
       </c>
+      <c r="J288" t="s">
+        <v>631</v>
+      </c>
       <c r="K288" t="s">
         <v>634</v>
       </c>
       <c r="L288" t="s">
         <v>635</v>
+      </c>
+      <c r="M288">
+        <v>0</v>
       </c>
       <c r="N288">
         <v>2</v>
@@ -17103,11 +17577,17 @@
       <c r="I289" t="s">
         <v>626</v>
       </c>
+      <c r="J289" t="s">
+        <v>631</v>
+      </c>
       <c r="K289" t="s">
         <v>634</v>
       </c>
       <c r="L289" t="s">
         <v>636</v>
+      </c>
+      <c r="M289">
+        <v>0</v>
       </c>
       <c r="N289">
         <v>2</v>
@@ -17150,11 +17630,17 @@
       <c r="I290" t="s">
         <v>626</v>
       </c>
+      <c r="J290" t="s">
+        <v>631</v>
+      </c>
       <c r="K290" t="s">
         <v>634</v>
       </c>
       <c r="L290" t="s">
         <v>635</v>
+      </c>
+      <c r="M290">
+        <v>0</v>
       </c>
       <c r="N290">
         <v>2</v>
@@ -17197,11 +17683,17 @@
       <c r="I291" t="s">
         <v>626</v>
       </c>
+      <c r="J291" t="s">
+        <v>631</v>
+      </c>
       <c r="K291" t="s">
         <v>633</v>
       </c>
       <c r="L291" t="s">
         <v>635</v>
+      </c>
+      <c r="M291">
+        <v>0</v>
       </c>
       <c r="N291">
         <v>2</v>
@@ -17244,11 +17736,17 @@
       <c r="I292" t="s">
         <v>626</v>
       </c>
+      <c r="J292" t="s">
+        <v>631</v>
+      </c>
       <c r="K292" t="s">
         <v>634</v>
       </c>
       <c r="L292" t="s">
         <v>635</v>
+      </c>
+      <c r="M292">
+        <v>0</v>
       </c>
       <c r="N292">
         <v>2</v>
@@ -17291,11 +17789,17 @@
       <c r="I293" t="s">
         <v>626</v>
       </c>
+      <c r="J293" t="s">
+        <v>631</v>
+      </c>
       <c r="K293" t="s">
         <v>634</v>
       </c>
       <c r="L293" t="s">
         <v>635</v>
+      </c>
+      <c r="M293">
+        <v>0</v>
       </c>
       <c r="N293">
         <v>2</v>
@@ -17338,11 +17842,17 @@
       <c r="I294" t="s">
         <v>626</v>
       </c>
+      <c r="J294" t="s">
+        <v>631</v>
+      </c>
       <c r="K294" t="s">
         <v>634</v>
       </c>
       <c r="L294" t="s">
         <v>635</v>
+      </c>
+      <c r="M294">
+        <v>0</v>
       </c>
       <c r="N294">
         <v>2</v>
@@ -17385,11 +17895,17 @@
       <c r="I295" t="s">
         <v>626</v>
       </c>
+      <c r="J295" t="s">
+        <v>631</v>
+      </c>
       <c r="K295" t="s">
         <v>634</v>
       </c>
       <c r="L295" t="s">
         <v>635</v>
+      </c>
+      <c r="M295">
+        <v>0</v>
       </c>
       <c r="N295">
         <v>2</v>
@@ -17432,11 +17948,17 @@
       <c r="I296" t="s">
         <v>626</v>
       </c>
+      <c r="J296" t="s">
+        <v>631</v>
+      </c>
       <c r="K296" t="s">
         <v>634</v>
       </c>
       <c r="L296" t="s">
         <v>635</v>
+      </c>
+      <c r="M296">
+        <v>0</v>
       </c>
       <c r="N296">
         <v>2</v>
@@ -17479,11 +18001,17 @@
       <c r="I297" t="s">
         <v>626</v>
       </c>
+      <c r="J297" t="s">
+        <v>631</v>
+      </c>
       <c r="K297" t="s">
         <v>633</v>
       </c>
       <c r="L297" t="s">
         <v>636</v>
+      </c>
+      <c r="M297">
+        <v>0</v>
       </c>
       <c r="N297">
         <v>2</v>
@@ -17526,11 +18054,17 @@
       <c r="I298" t="s">
         <v>626</v>
       </c>
+      <c r="J298" t="s">
+        <v>631</v>
+      </c>
       <c r="K298" t="s">
         <v>633</v>
       </c>
       <c r="L298" t="s">
         <v>635</v>
+      </c>
+      <c r="M298">
+        <v>0</v>
       </c>
       <c r="N298">
         <v>2</v>
@@ -17573,11 +18107,17 @@
       <c r="I299" t="s">
         <v>626</v>
       </c>
+      <c r="J299" t="s">
+        <v>631</v>
+      </c>
       <c r="K299" t="s">
         <v>633</v>
       </c>
       <c r="L299" t="s">
         <v>636</v>
+      </c>
+      <c r="M299">
+        <v>0</v>
       </c>
       <c r="N299">
         <v>2</v>
@@ -17620,11 +18160,17 @@
       <c r="I300" t="s">
         <v>626</v>
       </c>
+      <c r="J300" t="s">
+        <v>631</v>
+      </c>
       <c r="K300" t="s">
         <v>634</v>
       </c>
       <c r="L300" t="s">
         <v>635</v>
+      </c>
+      <c r="M300">
+        <v>0</v>
       </c>
       <c r="N300">
         <v>2</v>
@@ -17667,11 +18213,17 @@
       <c r="I301" t="s">
         <v>626</v>
       </c>
+      <c r="J301" t="s">
+        <v>631</v>
+      </c>
       <c r="K301" t="s">
         <v>634</v>
       </c>
       <c r="L301" t="s">
         <v>635</v>
+      </c>
+      <c r="M301">
+        <v>0</v>
       </c>
       <c r="N301">
         <v>2</v>
@@ -17714,11 +18266,17 @@
       <c r="I302" t="s">
         <v>626</v>
       </c>
+      <c r="J302" t="s">
+        <v>631</v>
+      </c>
       <c r="K302" t="s">
         <v>634</v>
       </c>
       <c r="L302" t="s">
         <v>635</v>
+      </c>
+      <c r="M302">
+        <v>0</v>
       </c>
       <c r="N302">
         <v>2</v>
@@ -17761,11 +18319,17 @@
       <c r="I303" t="s">
         <v>626</v>
       </c>
+      <c r="J303" t="s">
+        <v>631</v>
+      </c>
       <c r="K303" t="s">
         <v>633</v>
       </c>
       <c r="L303" t="s">
         <v>635</v>
+      </c>
+      <c r="M303">
+        <v>0</v>
       </c>
       <c r="N303">
         <v>2</v>
@@ -17808,11 +18372,17 @@
       <c r="I304" t="s">
         <v>626</v>
       </c>
+      <c r="J304" t="s">
+        <v>631</v>
+      </c>
       <c r="K304" t="s">
         <v>634</v>
       </c>
       <c r="L304" t="s">
         <v>635</v>
+      </c>
+      <c r="M304">
+        <v>0</v>
       </c>
       <c r="N304">
         <v>2</v>
@@ -17855,11 +18425,17 @@
       <c r="I305" t="s">
         <v>626</v>
       </c>
+      <c r="J305" t="s">
+        <v>631</v>
+      </c>
       <c r="K305" t="s">
         <v>634</v>
       </c>
       <c r="L305" t="s">
         <v>635</v>
+      </c>
+      <c r="M305">
+        <v>0</v>
       </c>
       <c r="N305">
         <v>2</v>
@@ -17902,11 +18478,17 @@
       <c r="I306" t="s">
         <v>626</v>
       </c>
+      <c r="J306" t="s">
+        <v>631</v>
+      </c>
       <c r="K306" t="s">
         <v>634</v>
       </c>
       <c r="L306" t="s">
         <v>635</v>
+      </c>
+      <c r="M306">
+        <v>0</v>
       </c>
       <c r="N306">
         <v>2</v>
@@ -17949,11 +18531,17 @@
       <c r="I307" t="s">
         <v>626</v>
       </c>
+      <c r="J307" t="s">
+        <v>631</v>
+      </c>
       <c r="K307" t="s">
         <v>633</v>
       </c>
       <c r="L307" t="s">
         <v>635</v>
+      </c>
+      <c r="M307">
+        <v>0</v>
       </c>
       <c r="N307">
         <v>2</v>
@@ -17996,11 +18584,17 @@
       <c r="I308" t="s">
         <v>626</v>
       </c>
+      <c r="J308" t="s">
+        <v>631</v>
+      </c>
       <c r="K308" t="s">
         <v>633</v>
       </c>
       <c r="L308" t="s">
         <v>636</v>
+      </c>
+      <c r="M308">
+        <v>0</v>
       </c>
       <c r="N308">
         <v>2</v>
@@ -18043,11 +18637,17 @@
       <c r="I309" t="s">
         <v>626</v>
       </c>
+      <c r="J309" t="s">
+        <v>631</v>
+      </c>
       <c r="K309" t="s">
         <v>634</v>
       </c>
       <c r="L309" t="s">
         <v>635</v>
+      </c>
+      <c r="M309">
+        <v>0</v>
       </c>
       <c r="N309">
         <v>2</v>
@@ -18090,11 +18690,17 @@
       <c r="I310" t="s">
         <v>626</v>
       </c>
+      <c r="J310" t="s">
+        <v>631</v>
+      </c>
       <c r="K310" t="s">
         <v>633</v>
       </c>
       <c r="L310" t="s">
         <v>636</v>
+      </c>
+      <c r="M310">
+        <v>0</v>
       </c>
       <c r="N310">
         <v>2</v>
@@ -18137,11 +18743,17 @@
       <c r="I311" t="s">
         <v>626</v>
       </c>
+      <c r="J311" t="s">
+        <v>631</v>
+      </c>
       <c r="K311" t="s">
         <v>634</v>
       </c>
       <c r="L311" t="s">
         <v>636</v>
+      </c>
+      <c r="M311">
+        <v>0</v>
       </c>
       <c r="N311">
         <v>2</v>
@@ -18184,11 +18796,17 @@
       <c r="I312" t="s">
         <v>626</v>
       </c>
+      <c r="J312" t="s">
+        <v>631</v>
+      </c>
       <c r="K312" t="s">
         <v>634</v>
       </c>
       <c r="L312" t="s">
         <v>636</v>
+      </c>
+      <c r="M312">
+        <v>0</v>
       </c>
       <c r="N312">
         <v>2</v>
@@ -18231,11 +18849,17 @@
       <c r="I313" t="s">
         <v>626</v>
       </c>
+      <c r="J313" t="s">
+        <v>631</v>
+      </c>
       <c r="K313" t="s">
         <v>634</v>
       </c>
       <c r="L313" t="s">
         <v>636</v>
+      </c>
+      <c r="M313">
+        <v>0</v>
       </c>
       <c r="N313">
         <v>2</v>
@@ -18278,11 +18902,17 @@
       <c r="I314" t="s">
         <v>626</v>
       </c>
+      <c r="J314" t="s">
+        <v>631</v>
+      </c>
       <c r="K314" t="s">
         <v>634</v>
       </c>
       <c r="L314" t="s">
         <v>635</v>
+      </c>
+      <c r="M314">
+        <v>0</v>
       </c>
       <c r="N314">
         <v>2</v>
@@ -18325,11 +18955,17 @@
       <c r="I315" t="s">
         <v>626</v>
       </c>
+      <c r="J315" t="s">
+        <v>631</v>
+      </c>
       <c r="K315" t="s">
         <v>634</v>
       </c>
       <c r="L315" t="s">
         <v>636</v>
+      </c>
+      <c r="M315">
+        <v>0</v>
       </c>
       <c r="N315">
         <v>2</v>
@@ -18372,11 +19008,17 @@
       <c r="I316" t="s">
         <v>626</v>
       </c>
+      <c r="J316" t="s">
+        <v>631</v>
+      </c>
       <c r="K316" t="s">
         <v>634</v>
       </c>
       <c r="L316" t="s">
         <v>635</v>
+      </c>
+      <c r="M316">
+        <v>0</v>
       </c>
       <c r="N316">
         <v>2</v>
@@ -18419,11 +19061,17 @@
       <c r="I317" t="s">
         <v>626</v>
       </c>
+      <c r="J317" t="s">
+        <v>631</v>
+      </c>
       <c r="K317" t="s">
         <v>634</v>
       </c>
       <c r="L317" t="s">
         <v>635</v>
+      </c>
+      <c r="M317">
+        <v>0</v>
       </c>
       <c r="N317">
         <v>2</v>
@@ -18466,11 +19114,17 @@
       <c r="I318" t="s">
         <v>626</v>
       </c>
+      <c r="J318" t="s">
+        <v>631</v>
+      </c>
       <c r="K318" t="s">
         <v>634</v>
       </c>
       <c r="L318" t="s">
         <v>636</v>
+      </c>
+      <c r="M318">
+        <v>0</v>
       </c>
       <c r="N318">
         <v>2</v>
@@ -18513,11 +19167,17 @@
       <c r="I319" t="s">
         <v>626</v>
       </c>
+      <c r="J319" t="s">
+        <v>631</v>
+      </c>
       <c r="K319" t="s">
         <v>634</v>
       </c>
       <c r="L319" t="s">
         <v>635</v>
+      </c>
+      <c r="M319">
+        <v>0</v>
       </c>
       <c r="N319">
         <v>2</v>
@@ -18560,11 +19220,17 @@
       <c r="I320" t="s">
         <v>626</v>
       </c>
+      <c r="J320" t="s">
+        <v>631</v>
+      </c>
       <c r="K320" t="s">
         <v>633</v>
       </c>
       <c r="L320" t="s">
         <v>635</v>
+      </c>
+      <c r="M320">
+        <v>0</v>
       </c>
       <c r="N320">
         <v>2</v>
@@ -18607,11 +19273,17 @@
       <c r="I321" t="s">
         <v>626</v>
       </c>
+      <c r="J321" t="s">
+        <v>631</v>
+      </c>
       <c r="K321" t="s">
         <v>634</v>
       </c>
       <c r="L321" t="s">
         <v>635</v>
+      </c>
+      <c r="M321">
+        <v>0</v>
       </c>
       <c r="N321">
         <v>2</v>
@@ -18654,11 +19326,17 @@
       <c r="I322" t="s">
         <v>626</v>
       </c>
+      <c r="J322" t="s">
+        <v>631</v>
+      </c>
       <c r="K322" t="s">
         <v>634</v>
       </c>
       <c r="L322" t="s">
         <v>636</v>
+      </c>
+      <c r="M322">
+        <v>0</v>
       </c>
       <c r="N322">
         <v>2</v>
@@ -18701,11 +19379,17 @@
       <c r="I323" t="s">
         <v>626</v>
       </c>
+      <c r="J323" t="s">
+        <v>631</v>
+      </c>
       <c r="K323" t="s">
         <v>634</v>
       </c>
       <c r="L323" t="s">
         <v>635</v>
+      </c>
+      <c r="M323">
+        <v>0</v>
       </c>
       <c r="N323">
         <v>2</v>
@@ -18748,11 +19432,17 @@
       <c r="I324" t="s">
         <v>626</v>
       </c>
+      <c r="J324" t="s">
+        <v>631</v>
+      </c>
       <c r="K324" t="s">
         <v>634</v>
       </c>
       <c r="L324" t="s">
         <v>636</v>
+      </c>
+      <c r="M324">
+        <v>0</v>
       </c>
       <c r="N324">
         <v>2</v>
@@ -18795,11 +19485,17 @@
       <c r="I325" t="s">
         <v>626</v>
       </c>
+      <c r="J325" t="s">
+        <v>631</v>
+      </c>
       <c r="K325" t="s">
         <v>634</v>
       </c>
       <c r="L325" t="s">
         <v>635</v>
+      </c>
+      <c r="M325">
+        <v>0</v>
       </c>
       <c r="N325">
         <v>2</v>
@@ -18842,11 +19538,17 @@
       <c r="I326" t="s">
         <v>626</v>
       </c>
+      <c r="J326" t="s">
+        <v>631</v>
+      </c>
       <c r="K326" t="s">
         <v>634</v>
       </c>
       <c r="L326" t="s">
         <v>636</v>
+      </c>
+      <c r="M326">
+        <v>0</v>
       </c>
       <c r="N326">
         <v>2</v>
@@ -18889,11 +19591,17 @@
       <c r="I327" t="s">
         <v>626</v>
       </c>
+      <c r="J327" t="s">
+        <v>631</v>
+      </c>
       <c r="K327" t="s">
         <v>634</v>
       </c>
       <c r="L327" t="s">
         <v>636</v>
+      </c>
+      <c r="M327">
+        <v>0</v>
       </c>
       <c r="N327">
         <v>2</v>
@@ -18936,11 +19644,17 @@
       <c r="I328" t="s">
         <v>626</v>
       </c>
+      <c r="J328" t="s">
+        <v>631</v>
+      </c>
       <c r="K328" t="s">
         <v>634</v>
       </c>
       <c r="L328" t="s">
         <v>636</v>
+      </c>
+      <c r="M328">
+        <v>0</v>
       </c>
       <c r="N328">
         <v>2</v>
@@ -18983,11 +19697,17 @@
       <c r="I329" t="s">
         <v>626</v>
       </c>
+      <c r="J329" t="s">
+        <v>631</v>
+      </c>
       <c r="K329" t="s">
         <v>634</v>
       </c>
       <c r="L329" t="s">
         <v>635</v>
+      </c>
+      <c r="M329">
+        <v>0</v>
       </c>
       <c r="N329">
         <v>2</v>
@@ -19030,11 +19750,17 @@
       <c r="I330" t="s">
         <v>626</v>
       </c>
+      <c r="J330" t="s">
+        <v>631</v>
+      </c>
       <c r="K330" t="s">
         <v>634</v>
       </c>
       <c r="L330" t="s">
         <v>636</v>
+      </c>
+      <c r="M330">
+        <v>0</v>
       </c>
       <c r="N330">
         <v>2</v>
@@ -19077,11 +19803,17 @@
       <c r="I331" t="s">
         <v>626</v>
       </c>
+      <c r="J331" t="s">
+        <v>631</v>
+      </c>
       <c r="K331" t="s">
         <v>633</v>
       </c>
       <c r="L331" t="s">
         <v>635</v>
+      </c>
+      <c r="M331">
+        <v>0</v>
       </c>
       <c r="N331">
         <v>2</v>
@@ -19124,11 +19856,17 @@
       <c r="I332" t="s">
         <v>626</v>
       </c>
+      <c r="J332" t="s">
+        <v>631</v>
+      </c>
       <c r="K332" t="s">
         <v>634</v>
       </c>
       <c r="L332" t="s">
         <v>635</v>
+      </c>
+      <c r="M332">
+        <v>0</v>
       </c>
       <c r="N332">
         <v>2</v>
@@ -19171,11 +19909,17 @@
       <c r="I333" t="s">
         <v>626</v>
       </c>
+      <c r="J333" t="s">
+        <v>631</v>
+      </c>
       <c r="K333" t="s">
         <v>634</v>
       </c>
       <c r="L333" t="s">
         <v>636</v>
+      </c>
+      <c r="M333">
+        <v>0</v>
       </c>
       <c r="N333">
         <v>2</v>
@@ -19219,7 +19963,7 @@
         <v>626</v>
       </c>
       <c r="J334" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K334" t="s">
         <v>633</v>
@@ -19272,7 +20016,7 @@
         <v>626</v>
       </c>
       <c r="J335" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K335" t="s">
         <v>634</v>
@@ -19748,11 +20492,17 @@
       <c r="I344" t="s">
         <v>626</v>
       </c>
+      <c r="J344" t="s">
+        <v>631</v>
+      </c>
       <c r="K344" t="s">
         <v>634</v>
       </c>
       <c r="L344" t="s">
         <v>636</v>
+      </c>
+      <c r="M344">
+        <v>0</v>
       </c>
       <c r="N344">
         <v>2</v>
@@ -19795,11 +20545,17 @@
       <c r="I345" t="s">
         <v>626</v>
       </c>
+      <c r="J345" t="s">
+        <v>631</v>
+      </c>
       <c r="K345" t="s">
         <v>633</v>
       </c>
       <c r="L345" t="s">
         <v>636</v>
+      </c>
+      <c r="M345">
+        <v>0</v>
       </c>
       <c r="N345">
         <v>2</v>
@@ -19843,7 +20599,7 @@
         <v>626</v>
       </c>
       <c r="J346" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="K346" t="s">
         <v>634</v>
@@ -19895,11 +20651,17 @@
       <c r="I347" t="s">
         <v>626</v>
       </c>
+      <c r="J347" t="s">
+        <v>631</v>
+      </c>
       <c r="K347" t="s">
         <v>634</v>
       </c>
       <c r="L347" t="s">
         <v>635</v>
+      </c>
+      <c r="M347">
+        <v>0</v>
       </c>
       <c r="N347">
         <v>2</v>
@@ -19942,11 +20704,17 @@
       <c r="I348" t="s">
         <v>626</v>
       </c>
+      <c r="J348" t="s">
+        <v>631</v>
+      </c>
       <c r="K348" t="s">
         <v>634</v>
       </c>
       <c r="L348" t="s">
         <v>635</v>
+      </c>
+      <c r="M348">
+        <v>0</v>
       </c>
       <c r="N348">
         <v>2</v>
@@ -19989,11 +20757,17 @@
       <c r="I349" t="s">
         <v>626</v>
       </c>
+      <c r="J349" t="s">
+        <v>631</v>
+      </c>
       <c r="K349" t="s">
         <v>634</v>
       </c>
       <c r="L349" t="s">
         <v>636</v>
+      </c>
+      <c r="M349">
+        <v>0</v>
       </c>
       <c r="N349">
         <v>2</v>
@@ -20036,11 +20810,17 @@
       <c r="I350" t="s">
         <v>626</v>
       </c>
+      <c r="J350" t="s">
+        <v>631</v>
+      </c>
       <c r="K350" t="s">
         <v>634</v>
       </c>
       <c r="L350" t="s">
         <v>636</v>
+      </c>
+      <c r="M350">
+        <v>0</v>
       </c>
       <c r="N350">
         <v>2</v>
@@ -20083,11 +20863,17 @@
       <c r="I351" t="s">
         <v>626</v>
       </c>
+      <c r="J351" t="s">
+        <v>631</v>
+      </c>
       <c r="K351" t="s">
         <v>634</v>
       </c>
       <c r="L351" t="s">
         <v>635</v>
+      </c>
+      <c r="M351">
+        <v>0</v>
       </c>
       <c r="N351">
         <v>2</v>
@@ -20130,11 +20916,17 @@
       <c r="I352" t="s">
         <v>626</v>
       </c>
+      <c r="J352" t="s">
+        <v>631</v>
+      </c>
       <c r="K352" t="s">
         <v>634</v>
       </c>
       <c r="L352" t="s">
         <v>635</v>
+      </c>
+      <c r="M352">
+        <v>0</v>
       </c>
       <c r="N352">
         <v>2</v>
@@ -20177,11 +20969,17 @@
       <c r="I353" t="s">
         <v>626</v>
       </c>
+      <c r="J353" t="s">
+        <v>631</v>
+      </c>
       <c r="K353" t="s">
         <v>634</v>
       </c>
       <c r="L353" t="s">
         <v>635</v>
+      </c>
+      <c r="M353">
+        <v>0</v>
       </c>
       <c r="N353">
         <v>2</v>
@@ -20224,11 +21022,17 @@
       <c r="I354" t="s">
         <v>626</v>
       </c>
+      <c r="J354" t="s">
+        <v>631</v>
+      </c>
       <c r="K354" t="s">
         <v>634</v>
       </c>
       <c r="L354" t="s">
         <v>635</v>
+      </c>
+      <c r="M354">
+        <v>0</v>
       </c>
       <c r="N354">
         <v>2</v>
@@ -20271,11 +21075,17 @@
       <c r="I355" t="s">
         <v>626</v>
       </c>
+      <c r="J355" t="s">
+        <v>631</v>
+      </c>
       <c r="K355" t="s">
         <v>634</v>
       </c>
       <c r="L355" t="s">
         <v>636</v>
+      </c>
+      <c r="M355">
+        <v>0</v>
       </c>
       <c r="N355">
         <v>2</v>
@@ -20318,11 +21128,17 @@
       <c r="I356" t="s">
         <v>626</v>
       </c>
+      <c r="J356" t="s">
+        <v>631</v>
+      </c>
       <c r="K356" t="s">
         <v>633</v>
       </c>
       <c r="L356" t="s">
         <v>635</v>
+      </c>
+      <c r="M356">
+        <v>0</v>
       </c>
       <c r="N356">
         <v>2</v>
@@ -20365,11 +21181,17 @@
       <c r="I357" t="s">
         <v>626</v>
       </c>
+      <c r="J357" t="s">
+        <v>631</v>
+      </c>
       <c r="K357" t="s">
         <v>634</v>
       </c>
       <c r="L357" t="s">
         <v>635</v>
+      </c>
+      <c r="M357">
+        <v>0</v>
       </c>
       <c r="N357">
         <v>2</v>
@@ -20412,11 +21234,17 @@
       <c r="I358" t="s">
         <v>626</v>
       </c>
+      <c r="J358" t="s">
+        <v>631</v>
+      </c>
       <c r="K358" t="s">
         <v>633</v>
       </c>
       <c r="L358" t="s">
         <v>636</v>
+      </c>
+      <c r="M358">
+        <v>0</v>
       </c>
       <c r="N358">
         <v>2</v>
@@ -20459,11 +21287,17 @@
       <c r="I359" t="s">
         <v>626</v>
       </c>
+      <c r="J359" t="s">
+        <v>631</v>
+      </c>
       <c r="K359" t="s">
         <v>634</v>
       </c>
       <c r="L359" t="s">
         <v>636</v>
+      </c>
+      <c r="M359">
+        <v>0</v>
       </c>
       <c r="N359">
         <v>2</v>
@@ -20506,11 +21340,17 @@
       <c r="I360" t="s">
         <v>626</v>
       </c>
+      <c r="J360" t="s">
+        <v>631</v>
+      </c>
       <c r="K360" t="s">
         <v>634</v>
       </c>
       <c r="L360" t="s">
         <v>636</v>
+      </c>
+      <c r="M360">
+        <v>0</v>
       </c>
       <c r="N360">
         <v>2</v>
@@ -20553,11 +21393,17 @@
       <c r="I361" t="s">
         <v>626</v>
       </c>
+      <c r="J361" t="s">
+        <v>631</v>
+      </c>
       <c r="K361" t="s">
         <v>633</v>
       </c>
       <c r="L361" t="s">
         <v>635</v>
+      </c>
+      <c r="M361">
+        <v>0</v>
       </c>
       <c r="N361">
         <v>2</v>
@@ -20600,11 +21446,17 @@
       <c r="I362" t="s">
         <v>626</v>
       </c>
+      <c r="J362" t="s">
+        <v>631</v>
+      </c>
       <c r="K362" t="s">
         <v>634</v>
       </c>
       <c r="L362" t="s">
         <v>635</v>
+      </c>
+      <c r="M362">
+        <v>0</v>
       </c>
       <c r="N362">
         <v>2</v>
@@ -20647,11 +21499,17 @@
       <c r="I363" t="s">
         <v>626</v>
       </c>
+      <c r="J363" t="s">
+        <v>631</v>
+      </c>
       <c r="K363" t="s">
         <v>633</v>
       </c>
       <c r="L363" t="s">
         <v>636</v>
+      </c>
+      <c r="M363">
+        <v>0</v>
       </c>
       <c r="N363">
         <v>2</v>
@@ -20694,11 +21552,17 @@
       <c r="I364" t="s">
         <v>626</v>
       </c>
+      <c r="J364" t="s">
+        <v>631</v>
+      </c>
       <c r="K364" t="s">
         <v>633</v>
       </c>
       <c r="L364" t="s">
         <v>635</v>
+      </c>
+      <c r="M364">
+        <v>0</v>
       </c>
       <c r="N364">
         <v>2</v>
@@ -20741,11 +21605,17 @@
       <c r="I365" t="s">
         <v>626</v>
       </c>
+      <c r="J365" t="s">
+        <v>631</v>
+      </c>
       <c r="K365" t="s">
         <v>634</v>
       </c>
       <c r="L365" t="s">
         <v>635</v>
+      </c>
+      <c r="M365">
+        <v>0</v>
       </c>
       <c r="N365">
         <v>2</v>
@@ -20788,11 +21658,17 @@
       <c r="I366" t="s">
         <v>626</v>
       </c>
+      <c r="J366" t="s">
+        <v>631</v>
+      </c>
       <c r="K366" t="s">
         <v>634</v>
       </c>
       <c r="L366" t="s">
         <v>635</v>
+      </c>
+      <c r="M366">
+        <v>0</v>
       </c>
       <c r="N366">
         <v>2</v>
@@ -20835,11 +21711,17 @@
       <c r="I367" t="s">
         <v>626</v>
       </c>
+      <c r="J367" t="s">
+        <v>631</v>
+      </c>
       <c r="K367" t="s">
         <v>634</v>
       </c>
       <c r="L367" t="s">
         <v>635</v>
+      </c>
+      <c r="M367">
+        <v>0</v>
       </c>
       <c r="N367">
         <v>2</v>
@@ -20882,11 +21764,17 @@
       <c r="I368" t="s">
         <v>626</v>
       </c>
+      <c r="J368" t="s">
+        <v>631</v>
+      </c>
       <c r="K368" t="s">
         <v>634</v>
       </c>
       <c r="L368" t="s">
         <v>636</v>
+      </c>
+      <c r="M368">
+        <v>0</v>
       </c>
       <c r="N368">
         <v>2</v>
@@ -20929,11 +21817,17 @@
       <c r="I369" t="s">
         <v>626</v>
       </c>
+      <c r="J369" t="s">
+        <v>631</v>
+      </c>
       <c r="K369" t="s">
         <v>634</v>
       </c>
       <c r="L369" t="s">
         <v>635</v>
+      </c>
+      <c r="M369">
+        <v>0</v>
       </c>
       <c r="N369">
         <v>1</v>
@@ -20976,11 +21870,17 @@
       <c r="I370" t="s">
         <v>626</v>
       </c>
+      <c r="J370" t="s">
+        <v>631</v>
+      </c>
       <c r="K370" t="s">
         <v>633</v>
       </c>
       <c r="L370" t="s">
         <v>635</v>
+      </c>
+      <c r="M370">
+        <v>0</v>
       </c>
       <c r="N370">
         <v>1</v>
@@ -21023,11 +21923,17 @@
       <c r="I371" t="s">
         <v>626</v>
       </c>
+      <c r="J371" t="s">
+        <v>631</v>
+      </c>
       <c r="K371" t="s">
         <v>634</v>
       </c>
       <c r="L371" t="s">
         <v>635</v>
+      </c>
+      <c r="M371">
+        <v>0</v>
       </c>
       <c r="N371">
         <v>1</v>
@@ -21070,11 +21976,17 @@
       <c r="I372" t="s">
         <v>626</v>
       </c>
+      <c r="J372" t="s">
+        <v>631</v>
+      </c>
       <c r="K372" t="s">
         <v>633</v>
       </c>
       <c r="L372" t="s">
         <v>635</v>
+      </c>
+      <c r="M372">
+        <v>0</v>
       </c>
       <c r="N372">
         <v>1</v>
@@ -21117,11 +22029,17 @@
       <c r="I373" t="s">
         <v>626</v>
       </c>
+      <c r="J373" t="s">
+        <v>631</v>
+      </c>
       <c r="K373" t="s">
         <v>634</v>
       </c>
       <c r="L373" t="s">
         <v>635</v>
+      </c>
+      <c r="M373">
+        <v>0</v>
       </c>
       <c r="N373">
         <v>1</v>
@@ -21164,11 +22082,17 @@
       <c r="I374" t="s">
         <v>626</v>
       </c>
+      <c r="J374" t="s">
+        <v>631</v>
+      </c>
       <c r="K374" t="s">
         <v>634</v>
       </c>
       <c r="L374" t="s">
         <v>635</v>
+      </c>
+      <c r="M374">
+        <v>0</v>
       </c>
       <c r="N374">
         <v>1</v>
@@ -21211,11 +22135,17 @@
       <c r="I375" t="s">
         <v>626</v>
       </c>
+      <c r="J375" t="s">
+        <v>631</v>
+      </c>
       <c r="K375" t="s">
         <v>634</v>
       </c>
       <c r="L375" t="s">
         <v>635</v>
+      </c>
+      <c r="M375">
+        <v>0</v>
       </c>
       <c r="N375">
         <v>1</v>
@@ -21258,11 +22188,17 @@
       <c r="I376" t="s">
         <v>626</v>
       </c>
+      <c r="J376" t="s">
+        <v>631</v>
+      </c>
       <c r="K376" t="s">
         <v>634</v>
       </c>
       <c r="L376" t="s">
         <v>636</v>
+      </c>
+      <c r="M376">
+        <v>0</v>
       </c>
       <c r="N376">
         <v>1</v>
@@ -21305,11 +22241,17 @@
       <c r="I377" t="s">
         <v>626</v>
       </c>
+      <c r="J377" t="s">
+        <v>631</v>
+      </c>
       <c r="K377" t="s">
         <v>634</v>
       </c>
       <c r="L377" t="s">
         <v>635</v>
+      </c>
+      <c r="M377">
+        <v>0</v>
       </c>
       <c r="N377">
         <v>1</v>
@@ -21352,11 +22294,17 @@
       <c r="I378" t="s">
         <v>626</v>
       </c>
+      <c r="J378" t="s">
+        <v>631</v>
+      </c>
       <c r="K378" t="s">
         <v>633</v>
       </c>
       <c r="L378" t="s">
         <v>635</v>
+      </c>
+      <c r="M378">
+        <v>0</v>
       </c>
       <c r="N378">
         <v>1</v>
@@ -21399,11 +22347,17 @@
       <c r="I379" t="s">
         <v>626</v>
       </c>
+      <c r="J379" t="s">
+        <v>631</v>
+      </c>
       <c r="K379" t="s">
         <v>633</v>
       </c>
       <c r="L379" t="s">
         <v>635</v>
+      </c>
+      <c r="M379">
+        <v>0</v>
       </c>
       <c r="N379">
         <v>1</v>
@@ -21446,11 +22400,17 @@
       <c r="I380" t="s">
         <v>626</v>
       </c>
+      <c r="J380" t="s">
+        <v>631</v>
+      </c>
       <c r="K380" t="s">
         <v>634</v>
       </c>
       <c r="L380" t="s">
         <v>635</v>
+      </c>
+      <c r="M380">
+        <v>0</v>
       </c>
       <c r="N380">
         <v>1</v>
@@ -21493,11 +22453,17 @@
       <c r="I381" t="s">
         <v>626</v>
       </c>
+      <c r="J381" t="s">
+        <v>631</v>
+      </c>
       <c r="K381" t="s">
         <v>634</v>
       </c>
       <c r="L381" t="s">
         <v>635</v>
+      </c>
+      <c r="M381">
+        <v>0</v>
       </c>
       <c r="N381">
         <v>1</v>
@@ -21540,11 +22506,17 @@
       <c r="I382" t="s">
         <v>626</v>
       </c>
+      <c r="J382" t="s">
+        <v>631</v>
+      </c>
       <c r="K382" t="s">
         <v>633</v>
       </c>
       <c r="L382" t="s">
         <v>635</v>
+      </c>
+      <c r="M382">
+        <v>0</v>
       </c>
       <c r="N382">
         <v>1</v>
@@ -21587,11 +22559,17 @@
       <c r="I383" t="s">
         <v>626</v>
       </c>
+      <c r="J383" t="s">
+        <v>631</v>
+      </c>
       <c r="K383" t="s">
         <v>634</v>
       </c>
       <c r="L383" t="s">
         <v>635</v>
+      </c>
+      <c r="M383">
+        <v>0</v>
       </c>
       <c r="N383">
         <v>1</v>
@@ -21634,11 +22612,17 @@
       <c r="I384" t="s">
         <v>626</v>
       </c>
+      <c r="J384" t="s">
+        <v>631</v>
+      </c>
       <c r="K384" t="s">
         <v>634</v>
       </c>
       <c r="L384" t="s">
         <v>635</v>
+      </c>
+      <c r="M384">
+        <v>0</v>
       </c>
       <c r="N384">
         <v>1</v>
@@ -21681,11 +22665,17 @@
       <c r="I385" t="s">
         <v>626</v>
       </c>
+      <c r="J385" t="s">
+        <v>631</v>
+      </c>
       <c r="K385" t="s">
         <v>634</v>
       </c>
       <c r="L385" t="s">
         <v>636</v>
+      </c>
+      <c r="M385">
+        <v>0</v>
       </c>
       <c r="N385">
         <v>1</v>
@@ -21728,11 +22718,17 @@
       <c r="I386" t="s">
         <v>626</v>
       </c>
+      <c r="J386" t="s">
+        <v>631</v>
+      </c>
       <c r="K386" t="s">
         <v>634</v>
       </c>
       <c r="L386" t="s">
         <v>635</v>
+      </c>
+      <c r="M386">
+        <v>0</v>
       </c>
       <c r="N386">
         <v>1</v>
@@ -21775,11 +22771,17 @@
       <c r="I387" t="s">
         <v>626</v>
       </c>
+      <c r="J387" t="s">
+        <v>631</v>
+      </c>
       <c r="K387" t="s">
         <v>634</v>
       </c>
       <c r="L387" t="s">
         <v>635</v>
+      </c>
+      <c r="M387">
+        <v>0</v>
       </c>
       <c r="N387">
         <v>1</v>
@@ -21822,11 +22824,17 @@
       <c r="I388" t="s">
         <v>626</v>
       </c>
+      <c r="J388" t="s">
+        <v>631</v>
+      </c>
       <c r="K388" t="s">
         <v>634</v>
       </c>
       <c r="L388" t="s">
         <v>635</v>
+      </c>
+      <c r="M388">
+        <v>0</v>
       </c>
       <c r="N388">
         <v>1</v>
@@ -21869,11 +22877,17 @@
       <c r="I389" t="s">
         <v>626</v>
       </c>
+      <c r="J389" t="s">
+        <v>631</v>
+      </c>
       <c r="K389" t="s">
         <v>633</v>
       </c>
       <c r="L389" t="s">
         <v>636</v>
+      </c>
+      <c r="M389">
+        <v>0</v>
       </c>
       <c r="N389">
         <v>1</v>
@@ -21916,11 +22930,17 @@
       <c r="I390" t="s">
         <v>626</v>
       </c>
+      <c r="J390" t="s">
+        <v>631</v>
+      </c>
       <c r="K390" t="s">
         <v>634</v>
       </c>
       <c r="L390" t="s">
         <v>636</v>
+      </c>
+      <c r="M390">
+        <v>0</v>
       </c>
       <c r="N390">
         <v>1</v>
@@ -21963,11 +22983,17 @@
       <c r="I391" t="s">
         <v>626</v>
       </c>
+      <c r="J391" t="s">
+        <v>631</v>
+      </c>
       <c r="K391" t="s">
         <v>634</v>
       </c>
       <c r="L391" t="s">
         <v>635</v>
+      </c>
+      <c r="M391">
+        <v>0</v>
       </c>
       <c r="N391">
         <v>1</v>
@@ -22010,11 +23036,17 @@
       <c r="I392" t="s">
         <v>626</v>
       </c>
+      <c r="J392" t="s">
+        <v>631</v>
+      </c>
       <c r="K392" t="s">
         <v>634</v>
       </c>
       <c r="L392" t="s">
         <v>635</v>
+      </c>
+      <c r="M392">
+        <v>0</v>
       </c>
       <c r="N392">
         <v>1</v>
@@ -22057,11 +23089,17 @@
       <c r="I393" t="s">
         <v>626</v>
       </c>
+      <c r="J393" t="s">
+        <v>631</v>
+      </c>
       <c r="K393" t="s">
         <v>634</v>
       </c>
       <c r="L393" t="s">
         <v>635</v>
+      </c>
+      <c r="M393">
+        <v>0</v>
       </c>
       <c r="N393">
         <v>1</v>
@@ -22104,11 +23142,17 @@
       <c r="I394" t="s">
         <v>626</v>
       </c>
+      <c r="J394" t="s">
+        <v>631</v>
+      </c>
       <c r="K394" t="s">
         <v>634</v>
       </c>
       <c r="L394" t="s">
         <v>635</v>
+      </c>
+      <c r="M394">
+        <v>0</v>
       </c>
       <c r="N394">
         <v>1</v>
@@ -22151,11 +23195,17 @@
       <c r="I395" t="s">
         <v>626</v>
       </c>
+      <c r="J395" t="s">
+        <v>631</v>
+      </c>
       <c r="K395" t="s">
         <v>634</v>
       </c>
       <c r="L395" t="s">
         <v>635</v>
+      </c>
+      <c r="M395">
+        <v>0</v>
       </c>
       <c r="N395">
         <v>1</v>
@@ -22198,11 +23248,17 @@
       <c r="I396" t="s">
         <v>626</v>
       </c>
+      <c r="J396" t="s">
+        <v>631</v>
+      </c>
       <c r="K396" t="s">
         <v>634</v>
       </c>
       <c r="L396" t="s">
         <v>635</v>
+      </c>
+      <c r="M396">
+        <v>0</v>
       </c>
       <c r="N396">
         <v>1</v>
@@ -22245,11 +23301,17 @@
       <c r="I397" t="s">
         <v>626</v>
       </c>
+      <c r="J397" t="s">
+        <v>631</v>
+      </c>
       <c r="K397" t="s">
         <v>634</v>
       </c>
       <c r="L397" t="s">
         <v>635</v>
+      </c>
+      <c r="M397">
+        <v>0</v>
       </c>
       <c r="N397">
         <v>1</v>
@@ -22292,11 +23354,17 @@
       <c r="I398" t="s">
         <v>626</v>
       </c>
+      <c r="J398" t="s">
+        <v>631</v>
+      </c>
       <c r="K398" t="s">
         <v>634</v>
       </c>
       <c r="L398" t="s">
         <v>635</v>
+      </c>
+      <c r="M398">
+        <v>0</v>
       </c>
       <c r="N398">
         <v>1</v>
@@ -22339,11 +23407,17 @@
       <c r="I399" t="s">
         <v>626</v>
       </c>
+      <c r="J399" t="s">
+        <v>631</v>
+      </c>
       <c r="K399" t="s">
         <v>634</v>
       </c>
       <c r="L399" t="s">
         <v>635</v>
+      </c>
+      <c r="M399">
+        <v>0</v>
       </c>
       <c r="N399">
         <v>1</v>
@@ -22386,11 +23460,17 @@
       <c r="I400" t="s">
         <v>626</v>
       </c>
+      <c r="J400" t="s">
+        <v>631</v>
+      </c>
       <c r="K400" t="s">
         <v>634</v>
       </c>
       <c r="L400" t="s">
         <v>635</v>
+      </c>
+      <c r="M400">
+        <v>0</v>
       </c>
       <c r="N400">
         <v>1</v>
@@ -22433,11 +23513,17 @@
       <c r="I401" t="s">
         <v>626</v>
       </c>
+      <c r="J401" t="s">
+        <v>631</v>
+      </c>
       <c r="K401" t="s">
         <v>634</v>
       </c>
       <c r="L401" t="s">
         <v>635</v>
+      </c>
+      <c r="M401">
+        <v>0</v>
       </c>
       <c r="N401">
         <v>1</v>
@@ -22480,11 +23566,17 @@
       <c r="I402" t="s">
         <v>626</v>
       </c>
+      <c r="J402" t="s">
+        <v>631</v>
+      </c>
       <c r="K402" t="s">
         <v>634</v>
       </c>
       <c r="L402" t="s">
         <v>636</v>
+      </c>
+      <c r="M402">
+        <v>0</v>
       </c>
       <c r="N402">
         <v>1</v>
@@ -22527,11 +23619,17 @@
       <c r="I403" t="s">
         <v>626</v>
       </c>
+      <c r="J403" t="s">
+        <v>631</v>
+      </c>
       <c r="K403" t="s">
         <v>633</v>
       </c>
       <c r="L403" t="s">
         <v>635</v>
+      </c>
+      <c r="M403">
+        <v>0</v>
       </c>
       <c r="N403">
         <v>1</v>
@@ -22574,11 +23672,17 @@
       <c r="I404" t="s">
         <v>626</v>
       </c>
+      <c r="J404" t="s">
+        <v>631</v>
+      </c>
       <c r="K404" t="s">
         <v>634</v>
       </c>
       <c r="L404" t="s">
         <v>635</v>
+      </c>
+      <c r="M404">
+        <v>0</v>
       </c>
       <c r="N404">
         <v>1</v>
@@ -22621,11 +23725,17 @@
       <c r="I405" t="s">
         <v>626</v>
       </c>
+      <c r="J405" t="s">
+        <v>631</v>
+      </c>
       <c r="K405" t="s">
         <v>634</v>
       </c>
       <c r="L405" t="s">
         <v>635</v>
+      </c>
+      <c r="M405">
+        <v>0</v>
       </c>
       <c r="N405">
         <v>1</v>
@@ -22668,11 +23778,17 @@
       <c r="I406" t="s">
         <v>626</v>
       </c>
+      <c r="J406" t="s">
+        <v>631</v>
+      </c>
       <c r="K406" t="s">
         <v>634</v>
       </c>
       <c r="L406" t="s">
         <v>635</v>
+      </c>
+      <c r="M406">
+        <v>0</v>
       </c>
       <c r="N406">
         <v>1</v>
@@ -22715,11 +23831,17 @@
       <c r="I407" t="s">
         <v>626</v>
       </c>
+      <c r="J407" t="s">
+        <v>631</v>
+      </c>
       <c r="K407" t="s">
         <v>634</v>
       </c>
       <c r="L407" t="s">
         <v>636</v>
+      </c>
+      <c r="M407">
+        <v>0</v>
       </c>
       <c r="N407">
         <v>1</v>
@@ -22762,11 +23884,17 @@
       <c r="I408" t="s">
         <v>626</v>
       </c>
+      <c r="J408" t="s">
+        <v>631</v>
+      </c>
       <c r="K408" t="s">
         <v>634</v>
       </c>
       <c r="L408" t="s">
         <v>636</v>
+      </c>
+      <c r="M408">
+        <v>0</v>
       </c>
       <c r="N408">
         <v>1</v>
@@ -22809,11 +23937,17 @@
       <c r="I409" t="s">
         <v>626</v>
       </c>
+      <c r="J409" t="s">
+        <v>631</v>
+      </c>
       <c r="K409" t="s">
         <v>634</v>
       </c>
       <c r="L409" t="s">
         <v>635</v>
+      </c>
+      <c r="M409">
+        <v>0</v>
       </c>
       <c r="N409">
         <v>1</v>
@@ -22856,11 +23990,17 @@
       <c r="I410" t="s">
         <v>626</v>
       </c>
+      <c r="J410" t="s">
+        <v>631</v>
+      </c>
       <c r="K410" t="s">
         <v>634</v>
       </c>
       <c r="L410" t="s">
         <v>635</v>
+      </c>
+      <c r="M410">
+        <v>0</v>
       </c>
       <c r="N410">
         <v>1</v>
@@ -22903,11 +24043,17 @@
       <c r="I411" t="s">
         <v>626</v>
       </c>
+      <c r="J411" t="s">
+        <v>631</v>
+      </c>
       <c r="K411" t="s">
         <v>634</v>
       </c>
       <c r="L411" t="s">
         <v>635</v>
+      </c>
+      <c r="M411">
+        <v>0</v>
       </c>
       <c r="N411">
         <v>1</v>
@@ -22950,11 +24096,17 @@
       <c r="I412" t="s">
         <v>626</v>
       </c>
+      <c r="J412" t="s">
+        <v>631</v>
+      </c>
       <c r="K412" t="s">
         <v>634</v>
       </c>
       <c r="L412" t="s">
         <v>635</v>
+      </c>
+      <c r="M412">
+        <v>0</v>
       </c>
       <c r="N412">
         <v>1</v>
@@ -22997,11 +24149,17 @@
       <c r="I413" t="s">
         <v>626</v>
       </c>
+      <c r="J413" t="s">
+        <v>631</v>
+      </c>
       <c r="K413" t="s">
         <v>634</v>
       </c>
       <c r="L413" t="s">
         <v>636</v>
+      </c>
+      <c r="M413">
+        <v>0</v>
       </c>
       <c r="N413">
         <v>1</v>
@@ -23044,11 +24202,17 @@
       <c r="I414" t="s">
         <v>626</v>
       </c>
+      <c r="J414" t="s">
+        <v>631</v>
+      </c>
       <c r="K414" t="s">
         <v>634</v>
       </c>
       <c r="L414" t="s">
         <v>635</v>
+      </c>
+      <c r="M414">
+        <v>0</v>
       </c>
       <c r="N414">
         <v>1</v>
@@ -23091,11 +24255,17 @@
       <c r="I415" t="s">
         <v>626</v>
       </c>
+      <c r="J415" t="s">
+        <v>631</v>
+      </c>
       <c r="K415" t="s">
         <v>634</v>
       </c>
       <c r="L415" t="s">
         <v>636</v>
+      </c>
+      <c r="M415">
+        <v>0</v>
       </c>
       <c r="N415">
         <v>1</v>
@@ -23138,11 +24308,17 @@
       <c r="I416" t="s">
         <v>626</v>
       </c>
+      <c r="J416" t="s">
+        <v>631</v>
+      </c>
       <c r="K416" t="s">
         <v>634</v>
       </c>
       <c r="L416" t="s">
         <v>636</v>
+      </c>
+      <c r="M416">
+        <v>0</v>
       </c>
       <c r="N416">
         <v>1</v>
@@ -23185,11 +24361,17 @@
       <c r="I417" t="s">
         <v>626</v>
       </c>
+      <c r="J417" t="s">
+        <v>631</v>
+      </c>
       <c r="K417" t="s">
         <v>634</v>
       </c>
       <c r="L417" t="s">
         <v>635</v>
+      </c>
+      <c r="M417">
+        <v>0</v>
       </c>
       <c r="N417">
         <v>1</v>
@@ -23232,11 +24414,17 @@
       <c r="I418" t="s">
         <v>626</v>
       </c>
+      <c r="J418" t="s">
+        <v>631</v>
+      </c>
       <c r="K418" t="s">
         <v>634</v>
       </c>
       <c r="L418" t="s">
         <v>636</v>
+      </c>
+      <c r="M418">
+        <v>0</v>
       </c>
       <c r="N418">
         <v>1</v>
@@ -23279,11 +24467,17 @@
       <c r="I419" t="s">
         <v>626</v>
       </c>
+      <c r="J419" t="s">
+        <v>631</v>
+      </c>
       <c r="K419" t="s">
         <v>634</v>
       </c>
       <c r="L419" t="s">
         <v>636</v>
+      </c>
+      <c r="M419">
+        <v>0</v>
       </c>
       <c r="N419">
         <v>1</v>
@@ -23326,11 +24520,17 @@
       <c r="I420" t="s">
         <v>626</v>
       </c>
+      <c r="J420" t="s">
+        <v>631</v>
+      </c>
       <c r="K420" t="s">
         <v>634</v>
       </c>
       <c r="L420" t="s">
         <v>635</v>
+      </c>
+      <c r="M420">
+        <v>0</v>
       </c>
       <c r="N420">
         <v>1</v>
@@ -23373,11 +24573,17 @@
       <c r="I421" t="s">
         <v>626</v>
       </c>
+      <c r="J421" t="s">
+        <v>631</v>
+      </c>
       <c r="K421" t="s">
         <v>634</v>
       </c>
       <c r="L421" t="s">
         <v>636</v>
+      </c>
+      <c r="M421">
+        <v>0</v>
       </c>
       <c r="N421">
         <v>1</v>
@@ -23420,11 +24626,17 @@
       <c r="I422" t="s">
         <v>626</v>
       </c>
+      <c r="J422" t="s">
+        <v>631</v>
+      </c>
       <c r="K422" t="s">
         <v>634</v>
       </c>
       <c r="L422" t="s">
         <v>635</v>
+      </c>
+      <c r="M422">
+        <v>0</v>
       </c>
       <c r="N422">
         <v>1</v>
@@ -23467,11 +24679,17 @@
       <c r="I423" t="s">
         <v>626</v>
       </c>
+      <c r="J423" t="s">
+        <v>631</v>
+      </c>
       <c r="K423" t="s">
         <v>634</v>
       </c>
       <c r="L423" t="s">
         <v>635</v>
+      </c>
+      <c r="M423">
+        <v>0</v>
       </c>
       <c r="N423">
         <v>1</v>
@@ -23514,11 +24732,17 @@
       <c r="I424" t="s">
         <v>626</v>
       </c>
+      <c r="J424" t="s">
+        <v>631</v>
+      </c>
       <c r="K424" t="s">
         <v>634</v>
       </c>
       <c r="L424" t="s">
         <v>635</v>
+      </c>
+      <c r="M424">
+        <v>0</v>
       </c>
       <c r="N424">
         <v>1</v>
@@ -23561,11 +24785,17 @@
       <c r="I425" t="s">
         <v>626</v>
       </c>
+      <c r="J425" t="s">
+        <v>631</v>
+      </c>
       <c r="K425" t="s">
         <v>634</v>
       </c>
       <c r="L425" t="s">
         <v>635</v>
+      </c>
+      <c r="M425">
+        <v>0</v>
       </c>
       <c r="N425">
         <v>1</v>
@@ -23608,11 +24838,17 @@
       <c r="I426" t="s">
         <v>626</v>
       </c>
+      <c r="J426" t="s">
+        <v>631</v>
+      </c>
       <c r="K426" t="s">
         <v>634</v>
       </c>
       <c r="L426" t="s">
         <v>635</v>
+      </c>
+      <c r="M426">
+        <v>0</v>
       </c>
       <c r="N426">
         <v>1</v>
@@ -23655,11 +24891,17 @@
       <c r="I427" t="s">
         <v>626</v>
       </c>
+      <c r="J427" t="s">
+        <v>631</v>
+      </c>
       <c r="K427" t="s">
         <v>634</v>
       </c>
       <c r="L427" t="s">
         <v>635</v>
+      </c>
+      <c r="M427">
+        <v>0</v>
       </c>
       <c r="N427">
         <v>1</v>
@@ -23702,11 +24944,17 @@
       <c r="I428" t="s">
         <v>626</v>
       </c>
+      <c r="J428" t="s">
+        <v>631</v>
+      </c>
       <c r="K428" t="s">
         <v>634</v>
       </c>
       <c r="L428" t="s">
         <v>635</v>
+      </c>
+      <c r="M428">
+        <v>0</v>
       </c>
       <c r="N428">
         <v>1</v>
@@ -23749,11 +24997,17 @@
       <c r="I429" t="s">
         <v>626</v>
       </c>
+      <c r="J429" t="s">
+        <v>631</v>
+      </c>
       <c r="K429" t="s">
         <v>634</v>
       </c>
       <c r="L429" t="s">
         <v>635</v>
+      </c>
+      <c r="M429">
+        <v>0</v>
       </c>
       <c r="N429">
         <v>1</v>
@@ -23796,11 +25050,17 @@
       <c r="I430" t="s">
         <v>626</v>
       </c>
+      <c r="J430" t="s">
+        <v>631</v>
+      </c>
       <c r="K430" t="s">
         <v>634</v>
       </c>
       <c r="L430" t="s">
         <v>635</v>
+      </c>
+      <c r="M430">
+        <v>0</v>
       </c>
       <c r="N430">
         <v>1</v>
@@ -23843,11 +25103,17 @@
       <c r="I431" t="s">
         <v>626</v>
       </c>
+      <c r="J431" t="s">
+        <v>631</v>
+      </c>
       <c r="K431" t="s">
         <v>634</v>
       </c>
       <c r="L431" t="s">
         <v>635</v>
+      </c>
+      <c r="M431">
+        <v>0</v>
       </c>
       <c r="N431">
         <v>1</v>
@@ -23890,11 +25156,17 @@
       <c r="I432" t="s">
         <v>626</v>
       </c>
+      <c r="J432" t="s">
+        <v>631</v>
+      </c>
       <c r="K432" t="s">
         <v>634</v>
       </c>
       <c r="L432" t="s">
         <v>636</v>
+      </c>
+      <c r="M432">
+        <v>0</v>
       </c>
       <c r="N432">
         <v>1</v>
@@ -23937,11 +25209,17 @@
       <c r="I433" t="s">
         <v>626</v>
       </c>
+      <c r="J433" t="s">
+        <v>631</v>
+      </c>
       <c r="K433" t="s">
         <v>634</v>
       </c>
       <c r="L433" t="s">
         <v>635</v>
+      </c>
+      <c r="M433">
+        <v>0</v>
       </c>
       <c r="N433">
         <v>1</v>
@@ -24037,11 +25315,17 @@
       <c r="I435" t="s">
         <v>626</v>
       </c>
+      <c r="J435" t="s">
+        <v>631</v>
+      </c>
       <c r="K435" t="s">
         <v>634</v>
       </c>
       <c r="L435" t="s">
         <v>636</v>
+      </c>
+      <c r="M435">
+        <v>0</v>
       </c>
       <c r="N435">
         <v>1</v>
@@ -24084,11 +25368,17 @@
       <c r="I436" t="s">
         <v>626</v>
       </c>
+      <c r="J436" t="s">
+        <v>631</v>
+      </c>
       <c r="K436" t="s">
         <v>634</v>
       </c>
       <c r="L436" t="s">
         <v>635</v>
+      </c>
+      <c r="M436">
+        <v>0</v>
       </c>
       <c r="N436">
         <v>1</v>
@@ -24131,11 +25421,17 @@
       <c r="I437" t="s">
         <v>626</v>
       </c>
+      <c r="J437" t="s">
+        <v>631</v>
+      </c>
       <c r="K437" t="s">
         <v>634</v>
       </c>
       <c r="L437" t="s">
         <v>635</v>
+      </c>
+      <c r="M437">
+        <v>0</v>
       </c>
       <c r="N437">
         <v>1</v>
@@ -24178,11 +25474,17 @@
       <c r="I438" t="s">
         <v>626</v>
       </c>
+      <c r="J438" t="s">
+        <v>631</v>
+      </c>
       <c r="K438" t="s">
         <v>634</v>
       </c>
       <c r="L438" t="s">
         <v>636</v>
+      </c>
+      <c r="M438">
+        <v>0</v>
       </c>
       <c r="N438">
         <v>1</v>
@@ -24225,11 +25527,17 @@
       <c r="I439" t="s">
         <v>626</v>
       </c>
+      <c r="J439" t="s">
+        <v>631</v>
+      </c>
       <c r="K439" t="s">
         <v>634</v>
       </c>
       <c r="L439" t="s">
         <v>635</v>
+      </c>
+      <c r="M439">
+        <v>0</v>
       </c>
       <c r="N439">
         <v>1</v>
@@ -24272,11 +25580,17 @@
       <c r="I440" t="s">
         <v>626</v>
       </c>
+      <c r="J440" t="s">
+        <v>631</v>
+      </c>
       <c r="K440" t="s">
         <v>634</v>
       </c>
       <c r="L440" t="s">
         <v>635</v>
+      </c>
+      <c r="M440">
+        <v>0</v>
       </c>
       <c r="N440">
         <v>1</v>
@@ -24319,11 +25633,17 @@
       <c r="I441" t="s">
         <v>626</v>
       </c>
+      <c r="J441" t="s">
+        <v>631</v>
+      </c>
       <c r="K441" t="s">
         <v>634</v>
       </c>
       <c r="L441" t="s">
         <v>635</v>
+      </c>
+      <c r="M441">
+        <v>0</v>
       </c>
       <c r="N441">
         <v>1</v>
@@ -24366,11 +25686,17 @@
       <c r="I442" t="s">
         <v>626</v>
       </c>
+      <c r="J442" t="s">
+        <v>631</v>
+      </c>
       <c r="K442" t="s">
         <v>634</v>
       </c>
       <c r="L442" t="s">
         <v>636</v>
+      </c>
+      <c r="M442">
+        <v>0</v>
       </c>
       <c r="N442">
         <v>1</v>
@@ -24413,11 +25739,17 @@
       <c r="I443" t="s">
         <v>626</v>
       </c>
+      <c r="J443" t="s">
+        <v>631</v>
+      </c>
       <c r="K443" t="s">
         <v>634</v>
       </c>
       <c r="L443" t="s">
         <v>636</v>
+      </c>
+      <c r="M443">
+        <v>0</v>
       </c>
       <c r="N443">
         <v>1</v>
@@ -24460,11 +25792,17 @@
       <c r="I444" t="s">
         <v>626</v>
       </c>
+      <c r="J444" t="s">
+        <v>631</v>
+      </c>
       <c r="K444" t="s">
         <v>634</v>
       </c>
       <c r="L444" t="s">
         <v>635</v>
+      </c>
+      <c r="M444">
+        <v>0</v>
       </c>
       <c r="N444">
         <v>1</v>
@@ -24507,11 +25845,17 @@
       <c r="I445" t="s">
         <v>626</v>
       </c>
+      <c r="J445" t="s">
+        <v>631</v>
+      </c>
       <c r="K445" t="s">
         <v>634</v>
       </c>
       <c r="L445" t="s">
         <v>635</v>
+      </c>
+      <c r="M445">
+        <v>0</v>
       </c>
       <c r="N445">
         <v>1</v>
@@ -24554,11 +25898,17 @@
       <c r="I446" t="s">
         <v>626</v>
       </c>
+      <c r="J446" t="s">
+        <v>631</v>
+      </c>
       <c r="K446" t="s">
         <v>634</v>
       </c>
       <c r="L446" t="s">
         <v>636</v>
+      </c>
+      <c r="M446">
+        <v>0</v>
       </c>
       <c r="N446">
         <v>1</v>
@@ -24601,11 +25951,17 @@
       <c r="I447" t="s">
         <v>626</v>
       </c>
+      <c r="J447" t="s">
+        <v>631</v>
+      </c>
       <c r="K447" t="s">
         <v>634</v>
       </c>
       <c r="L447" t="s">
         <v>636</v>
+      </c>
+      <c r="M447">
+        <v>0</v>
       </c>
       <c r="N447">
         <v>1</v>
@@ -24648,11 +26004,17 @@
       <c r="I448" t="s">
         <v>626</v>
       </c>
+      <c r="J448" t="s">
+        <v>631</v>
+      </c>
       <c r="K448" t="s">
         <v>634</v>
       </c>
       <c r="L448" t="s">
         <v>635</v>
+      </c>
+      <c r="M448">
+        <v>0</v>
       </c>
       <c r="N448">
         <v>1</v>
@@ -24695,11 +26057,17 @@
       <c r="I449" t="s">
         <v>626</v>
       </c>
+      <c r="J449" t="s">
+        <v>631</v>
+      </c>
       <c r="K449" t="s">
         <v>634</v>
       </c>
       <c r="L449" t="s">
         <v>635</v>
+      </c>
+      <c r="M449">
+        <v>0</v>
       </c>
       <c r="N449">
         <v>1</v>
@@ -24742,11 +26110,17 @@
       <c r="I450" t="s">
         <v>626</v>
       </c>
+      <c r="J450" t="s">
+        <v>631</v>
+      </c>
       <c r="K450" t="s">
         <v>634</v>
       </c>
       <c r="L450" t="s">
         <v>636</v>
+      </c>
+      <c r="M450">
+        <v>0</v>
       </c>
       <c r="N450">
         <v>1</v>
@@ -24789,11 +26163,17 @@
       <c r="I451" t="s">
         <v>626</v>
       </c>
+      <c r="J451" t="s">
+        <v>631</v>
+      </c>
       <c r="K451" t="s">
         <v>634</v>
       </c>
       <c r="L451" t="s">
         <v>636</v>
+      </c>
+      <c r="M451">
+        <v>0</v>
       </c>
       <c r="N451">
         <v>1</v>
@@ -24836,11 +26216,17 @@
       <c r="I452" t="s">
         <v>626</v>
       </c>
+      <c r="J452" t="s">
+        <v>631</v>
+      </c>
       <c r="K452" t="s">
         <v>633</v>
       </c>
       <c r="L452" t="s">
         <v>636</v>
+      </c>
+      <c r="M452">
+        <v>0</v>
       </c>
       <c r="N452">
         <v>1</v>
@@ -24883,11 +26269,17 @@
       <c r="I453" t="s">
         <v>626</v>
       </c>
+      <c r="J453" t="s">
+        <v>631</v>
+      </c>
       <c r="K453" t="s">
         <v>634</v>
       </c>
       <c r="L453" t="s">
         <v>636</v>
+      </c>
+      <c r="M453">
+        <v>0</v>
       </c>
       <c r="N453">
         <v>1</v>
@@ -24930,11 +26322,17 @@
       <c r="I454" t="s">
         <v>626</v>
       </c>
+      <c r="J454" t="s">
+        <v>631</v>
+      </c>
       <c r="K454" t="s">
         <v>634</v>
       </c>
       <c r="L454" t="s">
         <v>635</v>
+      </c>
+      <c r="M454">
+        <v>0</v>
       </c>
       <c r="N454">
         <v>1</v>
@@ -24977,11 +26375,17 @@
       <c r="I455" t="s">
         <v>626</v>
       </c>
+      <c r="J455" t="s">
+        <v>631</v>
+      </c>
       <c r="K455" t="s">
         <v>634</v>
       </c>
       <c r="L455" t="s">
         <v>635</v>
+      </c>
+      <c r="M455">
+        <v>0</v>
       </c>
       <c r="N455">
         <v>1</v>
@@ -25024,11 +26428,17 @@
       <c r="I456" t="s">
         <v>626</v>
       </c>
+      <c r="J456" t="s">
+        <v>631</v>
+      </c>
       <c r="K456" t="s">
         <v>634</v>
       </c>
       <c r="L456" t="s">
         <v>636</v>
+      </c>
+      <c r="M456">
+        <v>0</v>
       </c>
       <c r="N456">
         <v>1</v>
@@ -25071,11 +26481,17 @@
       <c r="I457" t="s">
         <v>626</v>
       </c>
+      <c r="J457" t="s">
+        <v>631</v>
+      </c>
       <c r="K457" t="s">
         <v>634</v>
       </c>
       <c r="L457" t="s">
         <v>636</v>
+      </c>
+      <c r="M457">
+        <v>0</v>
       </c>
       <c r="N457">
         <v>1</v>
@@ -25542,11 +26958,17 @@
       <c r="I466" t="s">
         <v>626</v>
       </c>
+      <c r="J466" t="s">
+        <v>631</v>
+      </c>
       <c r="K466" t="s">
         <v>634</v>
       </c>
       <c r="L466" t="s">
         <v>636</v>
+      </c>
+      <c r="M466">
+        <v>0</v>
       </c>
       <c r="N466">
         <v>1</v>
@@ -25589,11 +27011,17 @@
       <c r="I467" t="s">
         <v>626</v>
       </c>
+      <c r="J467" t="s">
+        <v>631</v>
+      </c>
       <c r="K467" t="s">
         <v>634</v>
       </c>
       <c r="L467" t="s">
         <v>636</v>
+      </c>
+      <c r="M467">
+        <v>0</v>
       </c>
       <c r="N467">
         <v>1</v>
@@ -25636,11 +27064,17 @@
       <c r="I468" t="s">
         <v>626</v>
       </c>
+      <c r="J468" t="s">
+        <v>631</v>
+      </c>
       <c r="K468" t="s">
         <v>634</v>
       </c>
       <c r="L468" t="s">
         <v>635</v>
+      </c>
+      <c r="M468">
+        <v>0</v>
       </c>
       <c r="N468">
         <v>1</v>
@@ -25683,11 +27117,17 @@
       <c r="I469" t="s">
         <v>626</v>
       </c>
+      <c r="J469" t="s">
+        <v>631</v>
+      </c>
       <c r="K469" t="s">
         <v>634</v>
       </c>
       <c r="L469" t="s">
         <v>635</v>
+      </c>
+      <c r="M469">
+        <v>0</v>
       </c>
       <c r="N469">
         <v>1</v>
@@ -25730,11 +27170,17 @@
       <c r="I470" t="s">
         <v>626</v>
       </c>
+      <c r="J470" t="s">
+        <v>631</v>
+      </c>
       <c r="K470" t="s">
         <v>634</v>
       </c>
       <c r="L470" t="s">
         <v>635</v>
+      </c>
+      <c r="M470">
+        <v>0</v>
       </c>
       <c r="N470">
         <v>1</v>
@@ -25777,11 +27223,17 @@
       <c r="I471" t="s">
         <v>626</v>
       </c>
+      <c r="J471" t="s">
+        <v>631</v>
+      </c>
       <c r="K471" t="s">
         <v>634</v>
       </c>
       <c r="L471" t="s">
         <v>635</v>
+      </c>
+      <c r="M471">
+        <v>0</v>
       </c>
       <c r="N471">
         <v>1</v>
@@ -25824,11 +27276,17 @@
       <c r="I472" t="s">
         <v>626</v>
       </c>
+      <c r="J472" t="s">
+        <v>631</v>
+      </c>
       <c r="K472" t="s">
         <v>634</v>
       </c>
       <c r="L472" t="s">
         <v>636</v>
+      </c>
+      <c r="M472">
+        <v>0</v>
       </c>
       <c r="N472">
         <v>1</v>
@@ -25871,11 +27329,17 @@
       <c r="I473" t="s">
         <v>626</v>
       </c>
+      <c r="J473" t="s">
+        <v>631</v>
+      </c>
       <c r="K473" t="s">
         <v>634</v>
       </c>
       <c r="L473" t="s">
         <v>636</v>
+      </c>
+      <c r="M473">
+        <v>0</v>
       </c>
       <c r="N473">
         <v>1</v>
@@ -25918,11 +27382,17 @@
       <c r="I474" t="s">
         <v>626</v>
       </c>
+      <c r="J474" t="s">
+        <v>631</v>
+      </c>
       <c r="K474" t="s">
         <v>634</v>
       </c>
       <c r="L474" t="s">
         <v>635</v>
+      </c>
+      <c r="M474">
+        <v>0</v>
       </c>
       <c r="N474">
         <v>1</v>
@@ -25965,11 +27435,17 @@
       <c r="I475" t="s">
         <v>626</v>
       </c>
+      <c r="J475" t="s">
+        <v>631</v>
+      </c>
       <c r="K475" t="s">
         <v>634</v>
       </c>
       <c r="L475" t="s">
         <v>635</v>
+      </c>
+      <c r="M475">
+        <v>0</v>
       </c>
       <c r="N475">
         <v>1</v>
@@ -26012,11 +27488,17 @@
       <c r="I476" t="s">
         <v>626</v>
       </c>
+      <c r="J476" t="s">
+        <v>631</v>
+      </c>
       <c r="K476" t="s">
         <v>634</v>
       </c>
       <c r="L476" t="s">
         <v>635</v>
+      </c>
+      <c r="M476">
+        <v>0</v>
       </c>
       <c r="N476">
         <v>1</v>
@@ -26059,11 +27541,17 @@
       <c r="I477" t="s">
         <v>626</v>
       </c>
+      <c r="J477" t="s">
+        <v>631</v>
+      </c>
       <c r="K477" t="s">
         <v>634</v>
       </c>
       <c r="L477" t="s">
         <v>635</v>
+      </c>
+      <c r="M477">
+        <v>0</v>
       </c>
       <c r="N477">
         <v>1</v>
@@ -26106,11 +27594,17 @@
       <c r="I478" t="s">
         <v>626</v>
       </c>
+      <c r="J478" t="s">
+        <v>631</v>
+      </c>
       <c r="K478" t="s">
         <v>634</v>
       </c>
       <c r="L478" t="s">
         <v>635</v>
+      </c>
+      <c r="M478">
+        <v>0</v>
       </c>
       <c r="N478">
         <v>1</v>
@@ -26153,11 +27647,17 @@
       <c r="I479" t="s">
         <v>626</v>
       </c>
+      <c r="J479" t="s">
+        <v>631</v>
+      </c>
       <c r="K479" t="s">
         <v>634</v>
       </c>
       <c r="L479" t="s">
         <v>636</v>
+      </c>
+      <c r="M479">
+        <v>0</v>
       </c>
       <c r="N479">
         <v>1</v>
@@ -26200,11 +27700,17 @@
       <c r="I480" t="s">
         <v>626</v>
       </c>
+      <c r="J480" t="s">
+        <v>631</v>
+      </c>
       <c r="K480" t="s">
         <v>634</v>
       </c>
       <c r="L480" t="s">
         <v>635</v>
+      </c>
+      <c r="M480">
+        <v>0</v>
       </c>
       <c r="N480">
         <v>1</v>
@@ -26247,11 +27753,17 @@
       <c r="I481" t="s">
         <v>626</v>
       </c>
+      <c r="J481" t="s">
+        <v>631</v>
+      </c>
       <c r="K481" t="s">
         <v>634</v>
       </c>
       <c r="L481" t="s">
         <v>635</v>
+      </c>
+      <c r="M481">
+        <v>0</v>
       </c>
       <c r="N481">
         <v>1</v>
@@ -26294,11 +27806,17 @@
       <c r="I482" t="s">
         <v>626</v>
       </c>
+      <c r="J482" t="s">
+        <v>631</v>
+      </c>
       <c r="K482" t="s">
         <v>634</v>
       </c>
       <c r="L482" t="s">
         <v>636</v>
+      </c>
+      <c r="M482">
+        <v>0</v>
       </c>
       <c r="N482">
         <v>1</v>
@@ -26341,11 +27859,17 @@
       <c r="I483" t="s">
         <v>626</v>
       </c>
+      <c r="J483" t="s">
+        <v>631</v>
+      </c>
       <c r="K483" t="s">
         <v>634</v>
       </c>
       <c r="L483" t="s">
         <v>636</v>
+      </c>
+      <c r="M483">
+        <v>0</v>
       </c>
       <c r="N483">
         <v>1</v>
@@ -26388,11 +27912,17 @@
       <c r="I484" t="s">
         <v>626</v>
       </c>
+      <c r="J484" t="s">
+        <v>631</v>
+      </c>
       <c r="K484" t="s">
         <v>634</v>
       </c>
       <c r="L484" t="s">
         <v>635</v>
+      </c>
+      <c r="M484">
+        <v>0</v>
       </c>
       <c r="N484">
         <v>1</v>
@@ -26435,11 +27965,17 @@
       <c r="I485" t="s">
         <v>626</v>
       </c>
+      <c r="J485" t="s">
+        <v>631</v>
+      </c>
       <c r="K485" t="s">
         <v>634</v>
       </c>
       <c r="L485" t="s">
         <v>635</v>
+      </c>
+      <c r="M485">
+        <v>0</v>
       </c>
       <c r="N485">
         <v>1</v>
@@ -26482,11 +28018,17 @@
       <c r="I486" t="s">
         <v>626</v>
       </c>
+      <c r="J486" t="s">
+        <v>631</v>
+      </c>
       <c r="K486" t="s">
         <v>634</v>
       </c>
       <c r="L486" t="s">
         <v>636</v>
+      </c>
+      <c r="M486">
+        <v>0</v>
       </c>
       <c r="N486">
         <v>1</v>
@@ -26529,11 +28071,17 @@
       <c r="I487" t="s">
         <v>626</v>
       </c>
+      <c r="J487" t="s">
+        <v>631</v>
+      </c>
       <c r="K487" t="s">
         <v>634</v>
       </c>
       <c r="L487" t="s">
         <v>636</v>
+      </c>
+      <c r="M487">
+        <v>0</v>
       </c>
       <c r="N487">
         <v>1</v>
@@ -26576,11 +28124,17 @@
       <c r="I488" t="s">
         <v>626</v>
       </c>
+      <c r="J488" t="s">
+        <v>631</v>
+      </c>
       <c r="K488" t="s">
         <v>634</v>
       </c>
       <c r="L488" t="s">
         <v>635</v>
+      </c>
+      <c r="M488">
+        <v>0</v>
       </c>
       <c r="N488">
         <v>1</v>
@@ -26623,11 +28177,17 @@
       <c r="I489" t="s">
         <v>626</v>
       </c>
+      <c r="J489" t="s">
+        <v>631</v>
+      </c>
       <c r="K489" t="s">
         <v>634</v>
       </c>
       <c r="L489" t="s">
         <v>635</v>
+      </c>
+      <c r="M489">
+        <v>0</v>
       </c>
       <c r="N489">
         <v>1</v>
@@ -26670,11 +28230,17 @@
       <c r="I490" t="s">
         <v>626</v>
       </c>
+      <c r="J490" t="s">
+        <v>631</v>
+      </c>
       <c r="K490" t="s">
         <v>634</v>
       </c>
       <c r="L490" t="s">
         <v>636</v>
+      </c>
+      <c r="M490">
+        <v>0</v>
       </c>
       <c r="N490">
         <v>1</v>
@@ -26717,11 +28283,17 @@
       <c r="I491" t="s">
         <v>626</v>
       </c>
+      <c r="J491" t="s">
+        <v>631</v>
+      </c>
       <c r="K491" t="s">
         <v>634</v>
       </c>
       <c r="L491" t="s">
         <v>635</v>
+      </c>
+      <c r="M491">
+        <v>0</v>
       </c>
       <c r="N491">
         <v>1</v>
@@ -26764,11 +28336,17 @@
       <c r="I492" t="s">
         <v>626</v>
       </c>
+      <c r="J492" t="s">
+        <v>631</v>
+      </c>
       <c r="K492" t="s">
         <v>634</v>
       </c>
       <c r="L492" t="s">
         <v>635</v>
+      </c>
+      <c r="M492">
+        <v>0</v>
       </c>
       <c r="N492">
         <v>1</v>
@@ -26811,11 +28389,17 @@
       <c r="I493" t="s">
         <v>626</v>
       </c>
+      <c r="J493" t="s">
+        <v>631</v>
+      </c>
       <c r="K493" t="s">
         <v>634</v>
       </c>
       <c r="L493" t="s">
         <v>635</v>
+      </c>
+      <c r="M493">
+        <v>0</v>
       </c>
       <c r="N493">
         <v>1</v>
@@ -26858,11 +28442,17 @@
       <c r="I494" t="s">
         <v>626</v>
       </c>
+      <c r="J494" t="s">
+        <v>631</v>
+      </c>
       <c r="K494" t="s">
         <v>634</v>
       </c>
       <c r="L494" t="s">
         <v>635</v>
+      </c>
+      <c r="M494">
+        <v>0</v>
       </c>
       <c r="N494">
         <v>1</v>
@@ -26905,11 +28495,17 @@
       <c r="I495" t="s">
         <v>626</v>
       </c>
+      <c r="J495" t="s">
+        <v>631</v>
+      </c>
       <c r="K495" t="s">
         <v>634</v>
       </c>
       <c r="L495" t="s">
         <v>635</v>
+      </c>
+      <c r="M495">
+        <v>0</v>
       </c>
       <c r="N495">
         <v>1</v>
@@ -26952,11 +28548,17 @@
       <c r="I496" t="s">
         <v>626</v>
       </c>
+      <c r="J496" t="s">
+        <v>631</v>
+      </c>
       <c r="K496" t="s">
         <v>634</v>
       </c>
       <c r="L496" t="s">
         <v>635</v>
+      </c>
+      <c r="M496">
+        <v>0</v>
       </c>
       <c r="N496">
         <v>1</v>
@@ -26999,11 +28601,17 @@
       <c r="I497" t="s">
         <v>626</v>
       </c>
+      <c r="J497" t="s">
+        <v>631</v>
+      </c>
       <c r="K497" t="s">
         <v>634</v>
       </c>
       <c r="L497" t="s">
         <v>636</v>
+      </c>
+      <c r="M497">
+        <v>0</v>
       </c>
       <c r="N497">
         <v>1</v>
@@ -27046,11 +28654,17 @@
       <c r="I498" t="s">
         <v>626</v>
       </c>
+      <c r="J498" t="s">
+        <v>631</v>
+      </c>
       <c r="K498" t="s">
         <v>634</v>
       </c>
       <c r="L498" t="s">
         <v>636</v>
+      </c>
+      <c r="M498">
+        <v>0</v>
       </c>
       <c r="N498">
         <v>1</v>
@@ -27093,11 +28707,17 @@
       <c r="I499" t="s">
         <v>626</v>
       </c>
+      <c r="J499" t="s">
+        <v>631</v>
+      </c>
       <c r="K499" t="s">
         <v>634</v>
       </c>
       <c r="L499" t="s">
         <v>635</v>
+      </c>
+      <c r="M499">
+        <v>0</v>
       </c>
       <c r="N499">
         <v>1</v>
